--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849963</v>
       </c>
       <c r="B2" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849964</v>
       </c>
       <c r="B3" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849965</v>
       </c>
       <c r="B4" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849966</v>
       </c>
       <c r="B5" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849967</v>
       </c>
       <c r="B6" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849968</v>
       </c>
       <c r="B7" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849969</v>
       </c>
       <c r="B8" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135849970</v>
       </c>
       <c r="B9" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135849971</v>
       </c>
       <c r="B10" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>99173</v>
+        <v>99175</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>110238</v>
+        <v>110240</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>135849989</v>
       </c>
       <c r="B53" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135849990</v>
       </c>
       <c r="B54" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>135849991</v>
       </c>
       <c r="B55" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>135849992</v>
       </c>
       <c r="B56" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>135849993</v>
       </c>
       <c r="B57" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>135849860</v>
       </c>
       <c r="B58" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>135849877</v>
       </c>
       <c r="B59" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135849878</v>
       </c>
       <c r="B60" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135850045</v>
       </c>
       <c r="B61" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>135849892</v>
       </c>
       <c r="B62" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>135850006</v>
       </c>
       <c r="B63" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>135850007</v>
       </c>
       <c r="B64" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>135850008</v>
       </c>
       <c r="B65" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>135849904</v>
       </c>
       <c r="B66" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>135849906</v>
       </c>
       <c r="B67" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>135849980</v>
       </c>
       <c r="B71" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ71"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135849969</v>
+        <v>135849970</v>
       </c>
       <c r="B8" t="n">
         <v>96488</v>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499958</v>
+        <v>499985</v>
       </c>
       <c r="R8" t="n">
-        <v>7003184</v>
+        <v>7003195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,6 +1429,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk med högörter.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1458,13 +1463,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849969</t>
+          <t>https://artportalen.se/Sighting/135849970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135849970</v>
+        <v>135849971</v>
       </c>
       <c r="B9" t="n">
         <v>96488</v>
@@ -1503,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499985</v>
+        <v>499984</v>
       </c>
       <c r="R9" t="n">
-        <v>7003195</v>
+        <v>7003226</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,11 +1546,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk med högörter.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1575,13 +1575,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849970</t>
+          <t>https://artportalen.se/Sighting/135849971</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849971</v>
+        <v>135849972</v>
       </c>
       <c r="B10" t="n">
         <v>96488</v>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499984</v>
+        <v>500084</v>
       </c>
       <c r="R10" t="n">
-        <v>7003226</v>
+        <v>7003324</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,44 +1687,43 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849971</t>
+          <t>https://artportalen.se/Sighting/135849972</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135849972</v>
+        <v>135850020</v>
       </c>
       <c r="B11" t="n">
-        <v>96488</v>
+        <v>79441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2812</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1732,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500084</v>
+        <v>500159</v>
       </c>
       <c r="R11" t="n">
-        <v>7003324</v>
+        <v>7003227</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,6 +1784,26 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1799,13 +1818,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849972</t>
+          <t>https://artportalen.se/Sighting/135850020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135850020</v>
+        <v>135850023</v>
       </c>
       <c r="B12" t="n">
         <v>79441</v>
@@ -1843,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500159</v>
+        <v>499977</v>
       </c>
       <c r="R12" t="n">
-        <v>7003227</v>
+        <v>7003248</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,54 +1949,63 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850020</t>
+          <t>https://artportalen.se/Sighting/135850023</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135850023</v>
+        <v>135849850</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499977</v>
+        <v>499952</v>
       </c>
       <c r="R13" t="n">
-        <v>7003248</v>
+        <v>7003158</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,13 +2040,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2039,12 +2071,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2061,54 +2093,63 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850023</t>
+          <t>https://artportalen.se/Sighting/135849850</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135850024</v>
+        <v>135849851</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500065</v>
+        <v>499941</v>
       </c>
       <c r="R14" t="n">
-        <v>7003294</v>
+        <v>7003178</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,13 +2184,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2168,9 +2213,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2187,54 +2237,63 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850024</t>
+          <t>https://artportalen.se/Sighting/135849851</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135850025</v>
+        <v>135849852</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500041</v>
+        <v>499932</v>
       </c>
       <c r="R15" t="n">
-        <v>7003432</v>
+        <v>7003181</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,13 +2328,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2296,12 +2359,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2318,58 +2381,63 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850025</t>
+          <t>https://artportalen.se/Sighting/135849852</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849875</v>
+        <v>135849853</v>
       </c>
       <c r="B16" t="n">
-        <v>80561</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500189</v>
+        <v>499931</v>
       </c>
       <c r="R16" t="n">
-        <v>7003310</v>
+        <v>7003183</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2404,13 +2472,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2421,22 +2493,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2453,13 +2525,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849875</t>
+          <t>https://artportalen.se/Sighting/135849853</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849850</v>
+        <v>135849854</v>
       </c>
       <c r="B17" t="n">
         <v>57980</v>
@@ -2506,10 +2578,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499952</v>
+        <v>499933</v>
       </c>
       <c r="R17" t="n">
-        <v>7003158</v>
+        <v>7003184</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2546,7 +2618,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), tydligt färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2597,13 +2669,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849850</t>
+          <t>https://artportalen.se/Sighting/135849854</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849851</v>
+        <v>135849855</v>
       </c>
       <c r="B18" t="n">
         <v>57980</v>
@@ -2650,10 +2722,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499941</v>
+        <v>499931</v>
       </c>
       <c r="R18" t="n">
-        <v>7003178</v>
+        <v>7003182</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2741,13 +2813,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849851</t>
+          <t>https://artportalen.se/Sighting/135849855</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849852</v>
+        <v>135849856</v>
       </c>
       <c r="B19" t="n">
         <v>57980</v>
@@ -2794,10 +2866,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499932</v>
+        <v>499927</v>
       </c>
       <c r="R19" t="n">
-        <v>7003181</v>
+        <v>7003186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2834,7 +2906,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,13 +2957,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849852</t>
+          <t>https://artportalen.se/Sighting/135849856</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849853</v>
+        <v>135849857</v>
       </c>
       <c r="B20" t="n">
         <v>57980</v>
@@ -2938,10 +3010,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499931</v>
+        <v>499918</v>
       </c>
       <c r="R20" t="n">
-        <v>7003183</v>
+        <v>7003193</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3029,13 +3101,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849853</t>
+          <t>https://artportalen.se/Sighting/135849857</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849854</v>
+        <v>135849858</v>
       </c>
       <c r="B21" t="n">
         <v>57980</v>
@@ -3082,10 +3154,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499933</v>
+        <v>499918</v>
       </c>
       <c r="R21" t="n">
-        <v>7003184</v>
+        <v>7003195</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3122,7 +3194,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), tydligt färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran vid en hyggeskant. Precis vid fyndplatsen observerades samtidigt en födosökande hane av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3173,13 +3245,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849854</t>
+          <t>https://artportalen.se/Sighting/135849858</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849855</v>
+        <v>135849859</v>
       </c>
       <c r="B22" t="n">
         <v>57980</v>
@@ -3207,12 +3279,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3229,7 +3309,7 @@
         <v>499931</v>
       </c>
       <c r="R22" t="n">
-        <v>7003182</v>
+        <v>7003195</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3266,7 +3346,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>1 hane som sågs födosöka på en stående död gran vid en hyggeskant. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3281,26 +3361,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3317,33 +3377,33 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849855</t>
+          <t>https://artportalen.se/Sighting/135849859</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849856</v>
+        <v>135849995</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>58239</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102981</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3351,12 +3411,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3370,10 +3434,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499927</v>
+        <v>500020</v>
       </c>
       <c r="R23" t="n">
-        <v>7003186</v>
+        <v>7003239</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3410,7 +3474,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 1 hussvala med lockläte flygandes över krontaket troligen även födosökande.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3425,26 +3489,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3461,63 +3505,67 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849856</t>
+          <t>https://artportalen.se/Sighting/135849995</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849857</v>
+        <v>135850013</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>99175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>219795</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499918</v>
+        <v>499967</v>
       </c>
       <c r="R24" t="n">
-        <v>7003193</v>
+        <v>7003224</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3552,17 +3600,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3571,24 +3615,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Rik på högörter.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3605,63 +3634,59 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849857</t>
+          <t>https://artportalen.se/Sighting/135850013</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849858</v>
+        <v>135849949</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>99614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499918</v>
+        <v>500041</v>
       </c>
       <c r="R25" t="n">
-        <v>7003195</v>
+        <v>7003256</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3698,7 +3723,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran vid en hyggeskant. Precis vid fyndplatsen observerades samtidigt en födosökande hane av tretåig hackspett.</t>
+          <t>Relativt rikligt med kransrams här.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3707,32 +3732,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3749,71 +3755,59 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849858</t>
+          <t>https://artportalen.se/Sighting/135849949</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849859</v>
+        <v>135849951</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>99614</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499931</v>
+        <v>499969</v>
       </c>
       <c r="R26" t="n">
-        <v>7003195</v>
+        <v>7003220</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3850,7 +3844,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 hane som sågs födosöka på en stående död gran vid en hyggeskant. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>I örtrikt stråk på fuktig mark.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3859,6 +3853,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3881,67 +3876,59 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849859</t>
+          <t>https://artportalen.se/Sighting/135849951</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849995</v>
+        <v>135849924</v>
       </c>
       <c r="B27" t="n">
-        <v>58239</v>
+        <v>108364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102981</v>
+        <v>220102</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500020</v>
+        <v>500117</v>
       </c>
       <c r="R27" t="n">
-        <v>7003239</v>
+        <v>7003169</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3976,17 +3963,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 1 hussvala med lockläte flygandes över krontaket troligen även födosökande.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4009,67 +3992,59 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849995</t>
+          <t>https://artportalen.se/Sighting/135849924</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849873</v>
+        <v>135849930</v>
       </c>
       <c r="B28" t="n">
-        <v>58141</v>
+        <v>108364</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220102</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499976</v>
+        <v>499972</v>
       </c>
       <c r="R28" t="n">
-        <v>7003189</v>
+        <v>7003221</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4110,17 +4085,13 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Flerskiktad barrblandskog med dominans av gran.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4137,16 +4108,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849873</t>
+          <t>https://artportalen.se/Sighting/135849930</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849867</v>
+        <v>135849931</v>
       </c>
       <c r="B29" t="n">
-        <v>58136</v>
+        <v>108364</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4154,50 +4125,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103023</v>
+        <v>220102</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500138</v>
+        <v>499953</v>
       </c>
       <c r="R29" t="n">
-        <v>7003230</v>
+        <v>7003186</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4232,17 +4195,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4265,16 +4224,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849867</t>
+          <t>https://artportalen.se/Sighting/135849931</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849869</v>
+        <v>135849932</v>
       </c>
       <c r="B30" t="n">
-        <v>58136</v>
+        <v>108364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4282,50 +4241,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103023</v>
+        <v>220102</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499966</v>
+        <v>499988</v>
       </c>
       <c r="R30" t="n">
-        <v>7003147</v>
+        <v>7003195</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4360,17 +4311,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4393,16 +4340,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849869</t>
+          <t>https://artportalen.se/Sighting/135849932</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135850013</v>
+        <v>135849933</v>
       </c>
       <c r="B31" t="n">
-        <v>99175</v>
+        <v>108364</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4410,33 +4357,25 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219795</v>
+        <v>220102</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -4450,10 +4389,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499967</v>
+        <v>499981</v>
       </c>
       <c r="R31" t="n">
-        <v>7003224</v>
+        <v>7003230</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4503,11 +4442,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Rik på högörter.</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4522,16 +4456,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850013</t>
+          <t>https://artportalen.se/Sighting/135849933</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849945</v>
+        <v>135849934</v>
       </c>
       <c r="B32" t="n">
-        <v>99614</v>
+        <v>108364</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4539,21 +4473,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4571,10 +4505,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500034</v>
+        <v>500067</v>
       </c>
       <c r="R32" t="n">
-        <v>7003139</v>
+        <v>7003318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4638,16 +4572,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849945</t>
+          <t>https://artportalen.se/Sighting/135849934</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849949</v>
+        <v>135849911</v>
       </c>
       <c r="B33" t="n">
-        <v>99614</v>
+        <v>111244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4655,21 +4589,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219880</v>
+        <v>220240</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4687,10 +4621,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500041</v>
+        <v>500133</v>
       </c>
       <c r="R33" t="n">
-        <v>7003256</v>
+        <v>7003286</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4725,11 +4659,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med kransrams här.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4759,16 +4688,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849949</t>
+          <t>https://artportalen.se/Sighting/135849911</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135849950</v>
+        <v>135849913</v>
       </c>
       <c r="B34" t="n">
-        <v>99614</v>
+        <v>111244</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4776,21 +4705,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219880</v>
+        <v>220240</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4808,10 +4737,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500064</v>
+        <v>499993</v>
       </c>
       <c r="R34" t="n">
-        <v>7003220</v>
+        <v>7003212</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4875,16 +4804,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849950</t>
+          <t>https://artportalen.se/Sighting/135849913</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135849951</v>
+        <v>135849914</v>
       </c>
       <c r="B35" t="n">
-        <v>99614</v>
+        <v>111244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4892,21 +4821,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219880</v>
+        <v>220240</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4924,10 +4853,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499969</v>
+        <v>500091</v>
       </c>
       <c r="R35" t="n">
-        <v>7003220</v>
+        <v>7003319</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4962,11 +4891,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>I örtrikt stråk på fuktig mark.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4996,45 +4920,53 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849951</t>
+          <t>https://artportalen.se/Sighting/135849914</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135850037</v>
+        <v>135849981</v>
       </c>
       <c r="B36" t="n">
-        <v>108294</v>
+        <v>99276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220083</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -5045,10 +4977,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500000</v>
+        <v>500163</v>
       </c>
       <c r="R36" t="n">
-        <v>7003248</v>
+        <v>7003324</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5083,6 +5015,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 7 blomställningar inom ca 2 x 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5112,45 +5049,53 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850037</t>
+          <t>https://artportalen.se/Sighting/135849981</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135850038</v>
+        <v>135849982</v>
       </c>
       <c r="B37" t="n">
-        <v>108294</v>
+        <v>99276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220083</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -5161,10 +5106,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500081</v>
+        <v>500144</v>
       </c>
       <c r="R37" t="n">
-        <v>7003252</v>
+        <v>7003322</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5199,6 +5144,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor och 1 blomställning inom ca 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5228,45 +5178,53 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850038</t>
+          <t>https://artportalen.se/Sighting/135849982</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849924</v>
+        <v>135849983</v>
       </c>
       <c r="B38" t="n">
-        <v>108364</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5277,10 +5235,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500117</v>
+        <v>500119</v>
       </c>
       <c r="R38" t="n">
-        <v>7003169</v>
+        <v>7003315</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5315,6 +5273,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5344,42 +5307,50 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849924</t>
+          <t>https://artportalen.se/Sighting/135849983</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849930</v>
+        <v>135849984</v>
       </c>
       <c r="B39" t="n">
-        <v>108364</v>
+        <v>99276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5393,10 +5364,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499972</v>
+        <v>500113</v>
       </c>
       <c r="R39" t="n">
-        <v>7003221</v>
+        <v>7003294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5431,6 +5402,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor och 1 blomställning inom ca 0,5 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5460,45 +5436,53 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849930</t>
+          <t>https://artportalen.se/Sighting/135849984</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849931</v>
+        <v>135849985</v>
       </c>
       <c r="B40" t="n">
-        <v>108364</v>
+        <v>99276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5509,10 +5493,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499953</v>
+        <v>500122</v>
       </c>
       <c r="R40" t="n">
-        <v>7003186</v>
+        <v>7003258</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5547,6 +5531,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor och 13 blomställningar inom ca 2 m2 yta i flerskiktad barrblandskog. "Marmorerade" blad med både ljusgröna och mörkare gröna färgnyanser.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5576,42 +5565,50 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849931</t>
+          <t>https://artportalen.se/Sighting/135849985</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135849932</v>
+        <v>135849989</v>
       </c>
       <c r="B41" t="n">
-        <v>108364</v>
+        <v>99276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -5625,10 +5622,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499988</v>
+        <v>499998</v>
       </c>
       <c r="R41" t="n">
-        <v>7003195</v>
+        <v>7003253</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5663,6 +5660,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Minst 8 plantor och 2 delvis överblommade blomställningar inom ca 1,5 m2 yta i en i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5692,42 +5694,50 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849932</t>
+          <t>https://artportalen.se/Sighting/135849989</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135849933</v>
+        <v>135849990</v>
       </c>
       <c r="B42" t="n">
-        <v>108364</v>
+        <v>99276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5741,10 +5751,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499981</v>
+        <v>499993</v>
       </c>
       <c r="R42" t="n">
-        <v>7003230</v>
+        <v>7003173</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5779,6 +5789,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor och 20 överblommade/blommande blomställningar inom ca 3 m2 yta i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5794,6 +5809,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
@@ -5808,45 +5828,53 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849933</t>
+          <t>https://artportalen.se/Sighting/135849990</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135849934</v>
+        <v>135849991</v>
       </c>
       <c r="B43" t="n">
-        <v>108364</v>
+        <v>99276</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5857,10 +5885,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500067</v>
+        <v>499998</v>
       </c>
       <c r="R43" t="n">
-        <v>7003318</v>
+        <v>7003174</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5895,6 +5923,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor och 18 blommande/överblommade blomställningar inom ca 5 m2 yta intill ett par aspar i en lucka i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5910,6 +5943,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad barrblandskog med tall, björk, asp, sälg och gråal.</t>
+        </is>
+      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
@@ -5924,45 +5962,53 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849934</t>
+          <t>https://artportalen.se/Sighting/135849991</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135849911</v>
+        <v>135849992</v>
       </c>
       <c r="B44" t="n">
-        <v>111244</v>
+        <v>99276</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -5973,10 +6019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500133</v>
+        <v>499978</v>
       </c>
       <c r="R44" t="n">
-        <v>7003286</v>
+        <v>7003240</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6011,6 +6057,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor och 5 överblommade blomställningar inom ca 1 m2 yta i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6040,59 +6091,71 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849911</t>
+          <t>https://artportalen.se/Sighting/135849992</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135849913</v>
+        <v>135849993</v>
       </c>
       <c r="B45" t="n">
-        <v>111244</v>
+        <v>99276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499993</v>
+        <v>500087</v>
       </c>
       <c r="R45" t="n">
-        <v>7003212</v>
+        <v>7003308</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6127,6 +6190,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor och 3 överblommade blomställningar inom ca 0,5 m2 yta i flerskiktad barrblandskog. Fint marmorerade blad med både ljusgröna och mörkgröna färgtoner.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6156,16 +6224,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849913</t>
+          <t>https://artportalen.se/Sighting/135849993</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135849914</v>
+        <v>135849860</v>
       </c>
       <c r="B46" t="n">
-        <v>111244</v>
+        <v>110014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6173,21 +6241,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220240</v>
+        <v>221184</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6205,10 +6273,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500091</v>
+        <v>499941</v>
       </c>
       <c r="R46" t="n">
-        <v>7003319</v>
+        <v>7003197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6272,16 +6340,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849914</t>
+          <t>https://artportalen.se/Sighting/135849860</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135850028</v>
+        <v>135850006</v>
       </c>
       <c r="B47" t="n">
-        <v>110240</v>
+        <v>98327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6289,28 +6357,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220294</v>
+        <v>223358</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6321,10 +6389,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499959</v>
+        <v>499967</v>
       </c>
       <c r="R47" t="n">
-        <v>7003236</v>
+        <v>7003113</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6371,7 +6439,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6388,53 +6456,45 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850028</t>
+          <t>https://artportalen.se/Sighting/135850006</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135849981</v>
+        <v>135850007</v>
       </c>
       <c r="B48" t="n">
-        <v>99276</v>
+        <v>98327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6445,10 +6505,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>500163</v>
+        <v>500037</v>
       </c>
       <c r="R48" t="n">
-        <v>7003324</v>
+        <v>7003192</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6483,11 +6543,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 7 blomställningar inom ca 2 x 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6517,53 +6572,45 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849981</t>
+          <t>https://artportalen.se/Sighting/135850007</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135849982</v>
+        <v>135850008</v>
       </c>
       <c r="B49" t="n">
-        <v>99276</v>
+        <v>98327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6574,10 +6621,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500144</v>
+        <v>499982</v>
       </c>
       <c r="R49" t="n">
-        <v>7003322</v>
+        <v>7003226</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6612,11 +6659,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor och 1 blomställning inom ca 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6646,50 +6688,42 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849982</t>
+          <t>https://artportalen.se/Sighting/135850008</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135849983</v>
+        <v>135849906</v>
       </c>
       <c r="B50" t="n">
-        <v>99276</v>
+        <v>101375</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>224885</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -6703,10 +6737,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>500119</v>
+        <v>500014</v>
       </c>
       <c r="R50" t="n">
-        <v>7003315</v>
+        <v>7003143</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6741,11 +6775,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 5 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6758,7 +6787,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6775,16 +6804,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849983</t>
+          <t>https://artportalen.se/Sighting/135849906</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135849984</v>
+        <v>135850019</v>
       </c>
       <c r="B51" t="n">
-        <v>99276</v>
+        <v>79441</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6792,39 +6821,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6832,10 +6848,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500113</v>
+        <v>500291</v>
       </c>
       <c r="R51" t="n">
-        <v>7003294</v>
+        <v>7003310</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6872,7 +6888,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 1 blomställning inom ca 0,5 m2 yta i barrblandskog.</t>
+          <t>Långväxta bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6890,6 +6906,26 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
@@ -6904,56 +6940,47 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849984</t>
+          <t>https://artportalen.se/Sighting/135850019</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135849985</v>
+        <v>135849907</v>
       </c>
       <c r="B52" t="n">
-        <v>99276</v>
+        <v>80556</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6961,10 +6988,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500122</v>
+        <v>500245</v>
       </c>
       <c r="R52" t="n">
-        <v>7003258</v>
+        <v>7003286</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7001,7 +7028,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 13 blomställningar inom ca 2 m2 yta i flerskiktad barrblandskog. "Marmorerade" blad med både ljusgröna och mörkare gröna färgnyanser.</t>
+          <t>Lunglav på 2 sälgar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7019,6 +7046,26 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
@@ -7033,13 +7080,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849985</t>
+          <t>https://artportalen.se/Sighting/135849907</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135849989</v>
+        <v>135849980</v>
       </c>
       <c r="B53" t="n">
         <v>99276</v>
@@ -7069,7 +7116,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7079,7 +7126,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -7090,10 +7137,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499998</v>
+        <v>500289</v>
       </c>
       <c r="R53" t="n">
-        <v>7003253</v>
+        <v>7003310</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7130,7 +7177,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 8 plantor och 2 delvis överblommade blomställningar inom ca 1,5 m2 yta i en i flerskiktad barrblandskog.</t>
+          <t>Minst 14 plantor och 5 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7161,2224 +7208,6 @@
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849989</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>135849990</v>
-      </c>
-      <c r="B54" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>499993</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7003173</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor och 20 överblommade/blommande blomställningar inom ca 3 m2 yta i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Flerskiktad barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849990</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>135849991</v>
-      </c>
-      <c r="B55" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>499998</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7003174</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor och 18 blommande/överblommade blomställningar inom ca 5 m2 yta intill ett par aspar i en lucka i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Grandominerad flerskiktad barrblandskog med tall, björk, asp, sälg och gråal.</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849991</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>135849992</v>
-      </c>
-      <c r="B56" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>499978</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7003240</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor och 5 överblommade blomställningar inom ca 1 m2 yta i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849992</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>135849993</v>
-      </c>
-      <c r="B57" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>500087</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7003308</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Minst 53 plantor och 3 överblommade blomställningar inom ca 0,5 m2 yta i flerskiktad barrblandskog. Fint marmorerade blad med både ljusgröna och mörkgröna färgtoner.</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849993</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>135849860</v>
-      </c>
-      <c r="B58" t="n">
-        <v>110014</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>499941</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7003197</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849860</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135849877</v>
-      </c>
-      <c r="B59" t="n">
-        <v>99298</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>499999</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7003182</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849877</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>135849878</v>
-      </c>
-      <c r="B60" t="n">
-        <v>99298</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>500072</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7003303</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849878</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>135850045</v>
-      </c>
-      <c r="B61" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>500086</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7003449</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850045</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>135849892</v>
-      </c>
-      <c r="B62" t="n">
-        <v>99082</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>499919</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7003193</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849892</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>135850006</v>
-      </c>
-      <c r="B63" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>499967</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7003113</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850006</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>135850007</v>
-      </c>
-      <c r="B64" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>500037</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7003192</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850007</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>135850008</v>
-      </c>
-      <c r="B65" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>499982</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7003226</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850008</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>135849904</v>
-      </c>
-      <c r="B66" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>500029</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7003136</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849904</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>135849906</v>
-      </c>
-      <c r="B67" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>500014</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7003143</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849906</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>135850019</v>
-      </c>
-      <c r="B68" t="n">
-        <v>79441</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>500291</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7003310</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran i barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850019</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135849907</v>
-      </c>
-      <c r="B69" t="n">
-        <v>80556</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>500245</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7003286</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Lunglav på 2 sälgar.</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849907</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135849870</v>
-      </c>
-      <c r="B70" t="n">
-        <v>58141</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>500305</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7003332</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849870</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135849980</v>
-      </c>
-      <c r="B71" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>500289</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7003310</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor och 5 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="inlineStr"/>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135849980</t>
         </is>
@@ -9438,24 +7267,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ53"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135849970</v>
+        <v>135849969</v>
       </c>
       <c r="B8" t="n">
         <v>96488</v>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499985</v>
+        <v>499958</v>
       </c>
       <c r="R8" t="n">
-        <v>7003195</v>
+        <v>7003184</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,11 +1429,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk med högörter.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1463,13 +1458,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849970</t>
+          <t>https://artportalen.se/Sighting/135849969</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135849971</v>
+        <v>135849970</v>
       </c>
       <c r="B9" t="n">
         <v>96488</v>
@@ -1508,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499984</v>
+        <v>499985</v>
       </c>
       <c r="R9" t="n">
-        <v>7003226</v>
+        <v>7003195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,6 +1541,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk med högörter.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1575,13 +1575,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849971</t>
+          <t>https://artportalen.se/Sighting/135849970</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849972</v>
+        <v>135849971</v>
       </c>
       <c r="B10" t="n">
         <v>96488</v>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500084</v>
+        <v>499984</v>
       </c>
       <c r="R10" t="n">
-        <v>7003324</v>
+        <v>7003226</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,43 +1687,44 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849972</t>
+          <t>https://artportalen.se/Sighting/135849971</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135850020</v>
+        <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>96488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500159</v>
+        <v>500084</v>
       </c>
       <c r="R11" t="n">
-        <v>7003227</v>
+        <v>7003324</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,26 +1785,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1818,13 +1799,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850020</t>
+          <t>https://artportalen.se/Sighting/135849972</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135850023</v>
+        <v>135850020</v>
       </c>
       <c r="B12" t="n">
         <v>79441</v>
@@ -1862,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499977</v>
+        <v>500159</v>
       </c>
       <c r="R12" t="n">
-        <v>7003248</v>
+        <v>7003227</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,63 +1930,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850023</t>
+          <t>https://artportalen.se/Sighting/135850020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135849850</v>
+        <v>135850023</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499952</v>
+        <v>499977</v>
       </c>
       <c r="R13" t="n">
-        <v>7003158</v>
+        <v>7003248</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,17 +2012,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2071,12 +2039,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2093,63 +2061,54 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849850</t>
+          <t>https://artportalen.se/Sighting/135850023</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849851</v>
+        <v>135850024</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499941</v>
+        <v>500065</v>
       </c>
       <c r="R14" t="n">
-        <v>7003178</v>
+        <v>7003294</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2184,17 +2143,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2213,14 +2168,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2237,63 +2187,54 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849851</t>
+          <t>https://artportalen.se/Sighting/135850024</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849852</v>
+        <v>135850025</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499932</v>
+        <v>500041</v>
       </c>
       <c r="R15" t="n">
-        <v>7003181</v>
+        <v>7003432</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2328,17 +2269,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2359,12 +2296,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2381,63 +2318,58 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849852</t>
+          <t>https://artportalen.se/Sighting/135850025</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849853</v>
+        <v>135849875</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>80561</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499931</v>
+        <v>500189</v>
       </c>
       <c r="R16" t="n">
-        <v>7003183</v>
+        <v>7003310</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2472,17 +2404,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2493,22 +2421,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2525,13 +2453,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849853</t>
+          <t>https://artportalen.se/Sighting/135849875</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849854</v>
+        <v>135849850</v>
       </c>
       <c r="B17" t="n">
         <v>57980</v>
@@ -2578,10 +2506,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499933</v>
+        <v>499952</v>
       </c>
       <c r="R17" t="n">
-        <v>7003184</v>
+        <v>7003158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2618,7 +2546,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), tydligt färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2669,13 +2597,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849854</t>
+          <t>https://artportalen.se/Sighting/135849850</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849855</v>
+        <v>135849851</v>
       </c>
       <c r="B18" t="n">
         <v>57980</v>
@@ -2722,10 +2650,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499931</v>
+        <v>499941</v>
       </c>
       <c r="R18" t="n">
-        <v>7003182</v>
+        <v>7003178</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2813,13 +2741,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849855</t>
+          <t>https://artportalen.se/Sighting/135849851</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849856</v>
+        <v>135849852</v>
       </c>
       <c r="B19" t="n">
         <v>57980</v>
@@ -2866,10 +2794,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499927</v>
+        <v>499932</v>
       </c>
       <c r="R19" t="n">
-        <v>7003186</v>
+        <v>7003181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2906,7 +2834,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2957,13 +2885,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849856</t>
+          <t>https://artportalen.se/Sighting/135849852</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849857</v>
+        <v>135849853</v>
       </c>
       <c r="B20" t="n">
         <v>57980</v>
@@ -3010,10 +2938,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499918</v>
+        <v>499931</v>
       </c>
       <c r="R20" t="n">
-        <v>7003193</v>
+        <v>7003183</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3101,13 +3029,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849857</t>
+          <t>https://artportalen.se/Sighting/135849853</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849858</v>
+        <v>135849854</v>
       </c>
       <c r="B21" t="n">
         <v>57980</v>
@@ -3154,10 +3082,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499918</v>
+        <v>499933</v>
       </c>
       <c r="R21" t="n">
-        <v>7003195</v>
+        <v>7003184</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3194,7 +3122,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran vid en hyggeskant. Precis vid fyndplatsen observerades samtidigt en födosökande hane av tretåig hackspett.</t>
+          <t>Ringhack (savhack), tydligt färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3245,13 +3173,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849858</t>
+          <t>https://artportalen.se/Sighting/135849854</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849859</v>
+        <v>135849855</v>
       </c>
       <c r="B22" t="n">
         <v>57980</v>
@@ -3279,20 +3207,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3309,7 +3229,7 @@
         <v>499931</v>
       </c>
       <c r="R22" t="n">
-        <v>7003195</v>
+        <v>7003182</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3346,7 +3266,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 hane som sågs födosöka på en stående död gran vid en hyggeskant. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3361,6 +3281,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3377,33 +3317,33 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849859</t>
+          <t>https://artportalen.se/Sighting/135849855</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849995</v>
+        <v>135849856</v>
       </c>
       <c r="B23" t="n">
-        <v>58239</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102981</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3411,16 +3351,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3434,10 +3370,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500020</v>
+        <v>499927</v>
       </c>
       <c r="R23" t="n">
-        <v>7003239</v>
+        <v>7003186</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3474,7 +3410,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 1 hussvala med lockläte flygandes över krontaket troligen även födosökande.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3489,6 +3425,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3505,67 +3461,63 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849995</t>
+          <t>https://artportalen.se/Sighting/135849856</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135850013</v>
+        <v>135849857</v>
       </c>
       <c r="B24" t="n">
-        <v>99175</v>
+        <v>57980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499967</v>
+        <v>499918</v>
       </c>
       <c r="R24" t="n">
-        <v>7003224</v>
+        <v>7003193</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3600,13 +3552,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3615,9 +3571,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Rik på högörter.</t>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3634,59 +3605,63 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850013</t>
+          <t>https://artportalen.se/Sighting/135849857</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849949</v>
+        <v>135849858</v>
       </c>
       <c r="B25" t="n">
-        <v>99614</v>
+        <v>57980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500041</v>
+        <v>499918</v>
       </c>
       <c r="R25" t="n">
-        <v>7003256</v>
+        <v>7003195</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3723,7 +3698,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Relativt rikligt med kransrams här.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran vid en hyggeskant. Precis vid fyndplatsen observerades samtidigt en födosökande hane av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3732,13 +3707,32 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3755,59 +3749,71 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849949</t>
+          <t>https://artportalen.se/Sighting/135849858</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849951</v>
+        <v>135849859</v>
       </c>
       <c r="B26" t="n">
-        <v>99614</v>
+        <v>57980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499969</v>
+        <v>499931</v>
       </c>
       <c r="R26" t="n">
-        <v>7003220</v>
+        <v>7003195</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3844,7 +3850,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I örtrikt stråk på fuktig mark.</t>
+          <t>1 hane som sågs födosöka på en stående död gran vid en hyggeskant. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3853,7 +3859,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3876,59 +3881,67 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849951</t>
+          <t>https://artportalen.se/Sighting/135849859</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849924</v>
+        <v>135849995</v>
       </c>
       <c r="B27" t="n">
-        <v>108364</v>
+        <v>58239</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220102</v>
+        <v>102981</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500117</v>
+        <v>500020</v>
       </c>
       <c r="R27" t="n">
-        <v>7003169</v>
+        <v>7003239</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3963,13 +3976,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 1 hussvala med lockläte flygandes över krontaket troligen även födosökande.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3992,59 +4009,67 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849924</t>
+          <t>https://artportalen.se/Sighting/135849995</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849930</v>
+        <v>135849873</v>
       </c>
       <c r="B28" t="n">
-        <v>108364</v>
+        <v>58141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220102</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499972</v>
+        <v>499976</v>
       </c>
       <c r="R28" t="n">
-        <v>7003221</v>
+        <v>7003189</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4085,13 +4110,17 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog med dominans av gran.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4108,16 +4137,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849930</t>
+          <t>https://artportalen.se/Sighting/135849873</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849931</v>
+        <v>135849867</v>
       </c>
       <c r="B29" t="n">
-        <v>108364</v>
+        <v>58136</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4125,42 +4154,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220102</v>
+        <v>103023</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499953</v>
+        <v>500138</v>
       </c>
       <c r="R29" t="n">
-        <v>7003186</v>
+        <v>7003230</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4195,13 +4232,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4224,16 +4265,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849931</t>
+          <t>https://artportalen.se/Sighting/135849867</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849932</v>
+        <v>135849869</v>
       </c>
       <c r="B30" t="n">
-        <v>108364</v>
+        <v>58136</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,42 +4282,50 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220102</v>
+        <v>103023</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499988</v>
+        <v>499966</v>
       </c>
       <c r="R30" t="n">
-        <v>7003195</v>
+        <v>7003147</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,13 +4360,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4340,16 +4393,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849932</t>
+          <t>https://artportalen.se/Sighting/135849869</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135849933</v>
+        <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>108364</v>
+        <v>99175</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4357,25 +4410,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220102</v>
+        <v>219795</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -4389,10 +4450,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499981</v>
+        <v>499967</v>
       </c>
       <c r="R31" t="n">
-        <v>7003230</v>
+        <v>7003224</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4442,6 +4503,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Rik på högörter.</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4456,16 +4522,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849933</t>
+          <t>https://artportalen.se/Sighting/135850013</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849934</v>
+        <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>108364</v>
+        <v>99614</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,21 +4539,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4505,10 +4571,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500067</v>
+        <v>500034</v>
       </c>
       <c r="R32" t="n">
-        <v>7003318</v>
+        <v>7003139</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4572,16 +4638,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849934</t>
+          <t>https://artportalen.se/Sighting/135849945</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849911</v>
+        <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>111244</v>
+        <v>99614</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,21 +4655,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220240</v>
+        <v>219880</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4621,10 +4687,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500133</v>
+        <v>500041</v>
       </c>
       <c r="R33" t="n">
-        <v>7003286</v>
+        <v>7003256</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4659,6 +4725,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med kransrams här.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4688,16 +4759,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849911</t>
+          <t>https://artportalen.se/Sighting/135849949</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135849913</v>
+        <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>111244</v>
+        <v>99614</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,21 +4776,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220240</v>
+        <v>219880</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4737,10 +4808,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499993</v>
+        <v>500064</v>
       </c>
       <c r="R34" t="n">
-        <v>7003212</v>
+        <v>7003220</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4804,16 +4875,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849913</t>
+          <t>https://artportalen.se/Sighting/135849950</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135849914</v>
+        <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>111244</v>
+        <v>99614</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,21 +4892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220240</v>
+        <v>219880</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4853,10 +4924,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500091</v>
+        <v>499969</v>
       </c>
       <c r="R35" t="n">
-        <v>7003319</v>
+        <v>7003220</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4891,6 +4962,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>I örtrikt stråk på fuktig mark.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4920,53 +4996,45 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849914</t>
+          <t>https://artportalen.se/Sighting/135849951</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135849981</v>
+        <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>99276</v>
+        <v>108294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4977,10 +5045,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500163</v>
+        <v>500000</v>
       </c>
       <c r="R36" t="n">
-        <v>7003324</v>
+        <v>7003248</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5015,11 +5083,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 7 blomställningar inom ca 2 x 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5049,53 +5112,45 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849981</t>
+          <t>https://artportalen.se/Sighting/135850037</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135849982</v>
+        <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>108294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -5106,10 +5161,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500144</v>
+        <v>500081</v>
       </c>
       <c r="R37" t="n">
-        <v>7003322</v>
+        <v>7003252</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5144,11 +5199,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor och 1 blomställning inom ca 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5178,53 +5228,45 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849982</t>
+          <t>https://artportalen.se/Sighting/135850038</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849983</v>
+        <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>108364</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5235,10 +5277,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500119</v>
+        <v>500117</v>
       </c>
       <c r="R38" t="n">
-        <v>7003315</v>
+        <v>7003169</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5273,11 +5315,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 5 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5307,50 +5344,42 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849983</t>
+          <t>https://artportalen.se/Sighting/135849924</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849984</v>
+        <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>99276</v>
+        <v>108364</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5364,10 +5393,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500113</v>
+        <v>499972</v>
       </c>
       <c r="R39" t="n">
-        <v>7003294</v>
+        <v>7003221</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5402,11 +5431,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor och 1 blomställning inom ca 0,5 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5436,53 +5460,45 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849984</t>
+          <t>https://artportalen.se/Sighting/135849930</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849985</v>
+        <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>99276</v>
+        <v>108364</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5493,10 +5509,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500122</v>
+        <v>499953</v>
       </c>
       <c r="R40" t="n">
-        <v>7003258</v>
+        <v>7003186</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5531,11 +5547,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst 50 plantor och 13 blomställningar inom ca 2 m2 yta i flerskiktad barrblandskog. "Marmorerade" blad med både ljusgröna och mörkare gröna färgnyanser.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5565,50 +5576,42 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849985</t>
+          <t>https://artportalen.se/Sighting/135849931</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135849989</v>
+        <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>99276</v>
+        <v>108364</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -5622,10 +5625,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499998</v>
+        <v>499988</v>
       </c>
       <c r="R41" t="n">
-        <v>7003253</v>
+        <v>7003195</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5660,11 +5663,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Minst 8 plantor och 2 delvis överblommade blomställningar inom ca 1,5 m2 yta i en i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5694,50 +5692,42 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849989</t>
+          <t>https://artportalen.se/Sighting/135849932</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135849990</v>
+        <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>99276</v>
+        <v>108364</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5751,10 +5741,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499993</v>
+        <v>499981</v>
       </c>
       <c r="R42" t="n">
-        <v>7003173</v>
+        <v>7003230</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5789,11 +5779,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor och 20 överblommade/blommande blomställningar inom ca 3 m2 yta i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5809,11 +5794,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
@@ -5828,53 +5808,45 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849990</t>
+          <t>https://artportalen.se/Sighting/135849933</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135849991</v>
+        <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>99276</v>
+        <v>108364</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5885,10 +5857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499998</v>
+        <v>500067</v>
       </c>
       <c r="R43" t="n">
-        <v>7003174</v>
+        <v>7003318</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5923,11 +5895,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor och 18 blommande/överblommade blomställningar inom ca 5 m2 yta intill ett par aspar i en lucka i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5943,11 +5910,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Grandominerad flerskiktad barrblandskog med tall, björk, asp, sälg och gråal.</t>
-        </is>
-      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
@@ -5962,53 +5924,45 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849991</t>
+          <t>https://artportalen.se/Sighting/135849934</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135849992</v>
+        <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>99276</v>
+        <v>111244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -6019,10 +5973,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499978</v>
+        <v>500133</v>
       </c>
       <c r="R44" t="n">
-        <v>7003240</v>
+        <v>7003286</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6057,11 +6011,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor och 5 överblommade blomställningar inom ca 1 m2 yta i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6091,71 +6040,59 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849992</t>
+          <t>https://artportalen.se/Sighting/135849911</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135849993</v>
+        <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>99276</v>
+        <v>111244</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500087</v>
+        <v>499993</v>
       </c>
       <c r="R45" t="n">
-        <v>7003308</v>
+        <v>7003212</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6190,11 +6127,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 53 plantor och 3 överblommade blomställningar inom ca 0,5 m2 yta i flerskiktad barrblandskog. Fint marmorerade blad med både ljusgröna och mörkgröna färgtoner.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6224,16 +6156,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849993</t>
+          <t>https://artportalen.se/Sighting/135849913</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135849860</v>
+        <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>110014</v>
+        <v>111244</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6241,21 +6173,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221184</v>
+        <v>220240</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6273,10 +6205,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499941</v>
+        <v>500091</v>
       </c>
       <c r="R46" t="n">
-        <v>7003197</v>
+        <v>7003319</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6340,16 +6272,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849860</t>
+          <t>https://artportalen.se/Sighting/135849914</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135850006</v>
+        <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>98327</v>
+        <v>110240</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6357,28 +6289,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223358</v>
+        <v>220294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6389,10 +6321,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499967</v>
+        <v>499959</v>
       </c>
       <c r="R47" t="n">
-        <v>7003113</v>
+        <v>7003236</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6439,7 +6371,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6456,45 +6388,53 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850006</t>
+          <t>https://artportalen.se/Sighting/135850028</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135850007</v>
+        <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>98327</v>
+        <v>99276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6505,10 +6445,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>500037</v>
+        <v>500163</v>
       </c>
       <c r="R48" t="n">
-        <v>7003192</v>
+        <v>7003324</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6543,6 +6483,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 7 blomställningar inom ca 2 x 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6572,45 +6517,53 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850007</t>
+          <t>https://artportalen.se/Sighting/135849981</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135850008</v>
+        <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>98327</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6621,10 +6574,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499982</v>
+        <v>500144</v>
       </c>
       <c r="R49" t="n">
-        <v>7003226</v>
+        <v>7003322</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6659,6 +6612,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor och 1 blomställning inom ca 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6688,42 +6646,50 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850008</t>
+          <t>https://artportalen.se/Sighting/135849982</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135849906</v>
+        <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>101375</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>224885</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -6737,10 +6703,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>500014</v>
+        <v>500119</v>
       </c>
       <c r="R50" t="n">
-        <v>7003143</v>
+        <v>7003315</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6775,6 +6741,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6787,7 +6758,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6804,16 +6775,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849906</t>
+          <t>https://artportalen.se/Sighting/135849983</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135850019</v>
+        <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>79441</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6821,26 +6792,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6848,10 +6832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500291</v>
+        <v>500113</v>
       </c>
       <c r="R51" t="n">
-        <v>7003310</v>
+        <v>7003294</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6888,7 +6872,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i barrblandskog.</t>
+          <t>Minst 22 plantor och 1 blomställning inom ca 0,5 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6906,26 +6890,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
@@ -6940,47 +6904,56 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850019</t>
+          <t>https://artportalen.se/Sighting/135849984</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135849907</v>
+        <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>80556</v>
+        <v>99276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6988,10 +6961,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500245</v>
+        <v>500122</v>
       </c>
       <c r="R52" t="n">
-        <v>7003286</v>
+        <v>7003258</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7028,7 +7001,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Lunglav på 2 sälgar.</t>
+          <t>Minst 50 plantor och 13 blomställningar inom ca 2 m2 yta i flerskiktad barrblandskog. "Marmorerade" blad med både ljusgröna och mörkare gröna färgnyanser.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7046,26 +7019,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
@@ -7080,13 +7033,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849907</t>
+          <t>https://artportalen.se/Sighting/135849985</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135849980</v>
+        <v>135849989</v>
       </c>
       <c r="B53" t="n">
         <v>99276</v>
@@ -7116,7 +7069,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7126,7 +7079,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -7137,10 +7090,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500289</v>
+        <v>499998</v>
       </c>
       <c r="R53" t="n">
-        <v>7003310</v>
+        <v>7003253</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7177,7 +7130,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 14 plantor och 5 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 8 plantor och 2 delvis överblommade blomställningar inom ca 1,5 m2 yta i en i flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7208,6 +7161,2224 @@
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849989</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135849990</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>499993</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7003173</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor och 20 överblommade/blommande blomställningar inom ca 3 m2 yta i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849990</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135849991</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>499998</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7003174</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor och 18 blommande/överblommade blomställningar inom ca 5 m2 yta intill ett par aspar i en lucka i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad barrblandskog med tall, björk, asp, sälg och gråal.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849991</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135849992</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>499978</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7003240</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor och 5 överblommade blomställningar inom ca 1 m2 yta i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849992</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135849993</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>500087</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7003308</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor och 3 överblommade blomställningar inom ca 0,5 m2 yta i flerskiktad barrblandskog. Fint marmorerade blad med både ljusgröna och mörkgröna färgtoner.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849993</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135849860</v>
+      </c>
+      <c r="B58" t="n">
+        <v>110014</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>499941</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7003197</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849860</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135849877</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>499999</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7003182</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849877</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135849878</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>500072</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7003303</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849878</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135850045</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>500086</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7003449</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850045</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135849892</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99082</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>499919</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7003193</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849892</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135850006</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>499967</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7003113</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850006</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135850007</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>500037</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7003192</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850007</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135850008</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>499982</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7003226</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850008</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135849904</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>500029</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7003136</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849904</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135849906</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>500014</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7003143</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849906</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135850019</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>500291</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7003310</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850019</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135849907</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>500245</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7003286</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Lunglav på 2 sälgar.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849907</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135849870</v>
+      </c>
+      <c r="B70" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>500305</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7003332</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849870</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135849980</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>500289</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7003310</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Minst 14 plantor och 5 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135849980</t>
         </is>
@@ -7267,6 +9438,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ71"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135849963</v>
       </c>
       <c r="B2" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849964</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849965</v>
       </c>
       <c r="B4" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849966</v>
       </c>
       <c r="B5" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849967</v>
       </c>
       <c r="B6" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849968</v>
       </c>
       <c r="B7" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135849969</v>
+        <v>135849970</v>
       </c>
       <c r="B8" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499958</v>
+        <v>499985</v>
       </c>
       <c r="R8" t="n">
-        <v>7003184</v>
+        <v>7003195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,6 +1429,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk med högörter.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1458,16 +1463,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849969</t>
+          <t>https://artportalen.se/Sighting/135849970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135849970</v>
+        <v>135849971</v>
       </c>
       <c r="B9" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499985</v>
+        <v>499984</v>
       </c>
       <c r="R9" t="n">
-        <v>7003195</v>
+        <v>7003226</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,11 +1546,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk med högörter.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1575,16 +1575,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849970</t>
+          <t>https://artportalen.se/Sighting/135849971</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849971</v>
+        <v>135849972</v>
       </c>
       <c r="B10" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499984</v>
+        <v>500084</v>
       </c>
       <c r="R10" t="n">
-        <v>7003226</v>
+        <v>7003324</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,44 +1687,43 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849971</t>
+          <t>https://artportalen.se/Sighting/135849972</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135849972</v>
+        <v>135850020</v>
       </c>
       <c r="B11" t="n">
-        <v>96488</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2812</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1732,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500084</v>
+        <v>500159</v>
       </c>
       <c r="R11" t="n">
-        <v>7003324</v>
+        <v>7003227</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,6 +1784,26 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1799,16 +1818,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849972</t>
+          <t>https://artportalen.se/Sighting/135850020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135850020</v>
+        <v>135850023</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500159</v>
+        <v>499977</v>
       </c>
       <c r="R12" t="n">
-        <v>7003227</v>
+        <v>7003248</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,54 +1949,63 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850020</t>
+          <t>https://artportalen.se/Sighting/135850023</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135850023</v>
+        <v>135849850</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499977</v>
+        <v>499952</v>
       </c>
       <c r="R13" t="n">
-        <v>7003248</v>
+        <v>7003158</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,13 +2040,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2039,12 +2071,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2061,54 +2093,63 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850023</t>
+          <t>https://artportalen.se/Sighting/135849850</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135850024</v>
+        <v>135849851</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500065</v>
+        <v>499941</v>
       </c>
       <c r="R14" t="n">
-        <v>7003294</v>
+        <v>7003178</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,13 +2184,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2168,9 +2213,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2187,54 +2237,63 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850024</t>
+          <t>https://artportalen.se/Sighting/135849851</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135850025</v>
+        <v>135849852</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500041</v>
+        <v>499932</v>
       </c>
       <c r="R15" t="n">
-        <v>7003432</v>
+        <v>7003181</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,13 +2328,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2296,12 +2359,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2318,58 +2381,63 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850025</t>
+          <t>https://artportalen.se/Sighting/135849852</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849875</v>
+        <v>135849853</v>
       </c>
       <c r="B16" t="n">
-        <v>80561</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500189</v>
+        <v>499931</v>
       </c>
       <c r="R16" t="n">
-        <v>7003310</v>
+        <v>7003183</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2404,13 +2472,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2421,22 +2493,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2453,16 +2525,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849875</t>
+          <t>https://artportalen.se/Sighting/135849853</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849850</v>
+        <v>135849854</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,10 +2578,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499952</v>
+        <v>499933</v>
       </c>
       <c r="R17" t="n">
-        <v>7003158</v>
+        <v>7003184</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2546,7 +2618,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), tydligt färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2597,16 +2669,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849850</t>
+          <t>https://artportalen.se/Sighting/135849854</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849851</v>
+        <v>135849855</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,10 +2722,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499941</v>
+        <v>499931</v>
       </c>
       <c r="R18" t="n">
-        <v>7003178</v>
+        <v>7003182</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2741,16 +2813,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849851</t>
+          <t>https://artportalen.se/Sighting/135849855</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849852</v>
+        <v>135849856</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2794,10 +2866,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499932</v>
+        <v>499927</v>
       </c>
       <c r="R19" t="n">
-        <v>7003181</v>
+        <v>7003186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2834,7 +2906,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,16 +2957,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849852</t>
+          <t>https://artportalen.se/Sighting/135849856</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849853</v>
+        <v>135849857</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2938,10 +3010,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499931</v>
+        <v>499918</v>
       </c>
       <c r="R20" t="n">
-        <v>7003183</v>
+        <v>7003193</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3029,16 +3101,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849853</t>
+          <t>https://artportalen.se/Sighting/135849857</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849854</v>
+        <v>135849858</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3082,10 +3154,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499933</v>
+        <v>499918</v>
       </c>
       <c r="R21" t="n">
-        <v>7003184</v>
+        <v>7003195</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3122,7 +3194,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), tydligt färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran vid en hyggeskant. Precis vid fyndplatsen observerades samtidigt en födosökande hane av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3173,16 +3245,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849854</t>
+          <t>https://artportalen.se/Sighting/135849858</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849855</v>
+        <v>135849859</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3207,12 +3279,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3229,7 +3309,7 @@
         <v>499931</v>
       </c>
       <c r="R22" t="n">
-        <v>7003182</v>
+        <v>7003195</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3266,7 +3346,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>1 hane som sågs födosöka på en stående död gran vid en hyggeskant. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3281,26 +3361,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3317,33 +3377,33 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849855</t>
+          <t>https://artportalen.se/Sighting/135849859</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849856</v>
+        <v>135849995</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>58241</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102981</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3351,12 +3411,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3370,10 +3434,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499927</v>
+        <v>500020</v>
       </c>
       <c r="R23" t="n">
-        <v>7003186</v>
+        <v>7003239</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3410,7 +3474,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 1 hussvala med lockläte flygandes över krontaket troligen även födosökande.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3425,26 +3489,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3461,63 +3505,67 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849856</t>
+          <t>https://artportalen.se/Sighting/135849995</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849857</v>
+        <v>135850013</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>99192</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>219795</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499918</v>
+        <v>499967</v>
       </c>
       <c r="R24" t="n">
-        <v>7003193</v>
+        <v>7003224</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3552,17 +3600,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3571,24 +3615,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Rik på högörter.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3605,63 +3634,59 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849857</t>
+          <t>https://artportalen.se/Sighting/135850013</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849858</v>
+        <v>135849949</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>99631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499918</v>
+        <v>500041</v>
       </c>
       <c r="R25" t="n">
-        <v>7003195</v>
+        <v>7003256</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3698,7 +3723,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran vid en hyggeskant. Precis vid fyndplatsen observerades samtidigt en födosökande hane av tretåig hackspett.</t>
+          <t>Relativt rikligt med kransrams här.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3707,32 +3732,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3749,71 +3755,59 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849858</t>
+          <t>https://artportalen.se/Sighting/135849949</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849859</v>
+        <v>135849951</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>99631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499931</v>
+        <v>499969</v>
       </c>
       <c r="R26" t="n">
-        <v>7003195</v>
+        <v>7003220</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3850,7 +3844,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 hane som sågs födosöka på en stående död gran vid en hyggeskant. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>I örtrikt stråk på fuktig mark.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3859,6 +3853,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3881,67 +3876,59 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849859</t>
+          <t>https://artportalen.se/Sighting/135849951</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849995</v>
+        <v>135849924</v>
       </c>
       <c r="B27" t="n">
-        <v>58239</v>
+        <v>108387</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102981</v>
+        <v>220102</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500020</v>
+        <v>500117</v>
       </c>
       <c r="R27" t="n">
-        <v>7003239</v>
+        <v>7003169</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3976,17 +3963,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 1 hussvala med lockläte flygandes över krontaket troligen även födosökande.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4009,67 +3992,59 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849995</t>
+          <t>https://artportalen.se/Sighting/135849924</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849873</v>
+        <v>135849930</v>
       </c>
       <c r="B28" t="n">
-        <v>58141</v>
+        <v>108387</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220102</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499976</v>
+        <v>499972</v>
       </c>
       <c r="R28" t="n">
-        <v>7003189</v>
+        <v>7003221</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4110,17 +4085,13 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Flerskiktad barrblandskog med dominans av gran.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4137,16 +4108,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849873</t>
+          <t>https://artportalen.se/Sighting/135849930</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849867</v>
+        <v>135849931</v>
       </c>
       <c r="B29" t="n">
-        <v>58136</v>
+        <v>108387</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4154,50 +4125,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103023</v>
+        <v>220102</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500138</v>
+        <v>499953</v>
       </c>
       <c r="R29" t="n">
-        <v>7003230</v>
+        <v>7003186</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4232,17 +4195,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4265,16 +4224,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849867</t>
+          <t>https://artportalen.se/Sighting/135849931</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849869</v>
+        <v>135849932</v>
       </c>
       <c r="B30" t="n">
-        <v>58136</v>
+        <v>108387</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4282,50 +4241,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103023</v>
+        <v>220102</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499966</v>
+        <v>499988</v>
       </c>
       <c r="R30" t="n">
-        <v>7003147</v>
+        <v>7003195</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4360,17 +4311,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4393,16 +4340,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849869</t>
+          <t>https://artportalen.se/Sighting/135849932</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135850013</v>
+        <v>135849933</v>
       </c>
       <c r="B31" t="n">
-        <v>99175</v>
+        <v>108387</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4410,33 +4357,25 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219795</v>
+        <v>220102</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -4450,10 +4389,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499967</v>
+        <v>499981</v>
       </c>
       <c r="R31" t="n">
-        <v>7003224</v>
+        <v>7003230</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4503,11 +4442,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Rik på högörter.</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4522,16 +4456,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850013</t>
+          <t>https://artportalen.se/Sighting/135849933</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849945</v>
+        <v>135849934</v>
       </c>
       <c r="B32" t="n">
-        <v>99614</v>
+        <v>108387</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4539,21 +4473,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4571,10 +4505,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500034</v>
+        <v>500067</v>
       </c>
       <c r="R32" t="n">
-        <v>7003139</v>
+        <v>7003318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4638,16 +4572,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849945</t>
+          <t>https://artportalen.se/Sighting/135849934</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849949</v>
+        <v>135849911</v>
       </c>
       <c r="B33" t="n">
-        <v>99614</v>
+        <v>111267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4655,21 +4589,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219880</v>
+        <v>220240</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4687,10 +4621,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500041</v>
+        <v>500133</v>
       </c>
       <c r="R33" t="n">
-        <v>7003256</v>
+        <v>7003286</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4725,11 +4659,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med kransrams här.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4759,16 +4688,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849949</t>
+          <t>https://artportalen.se/Sighting/135849911</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135849950</v>
+        <v>135849913</v>
       </c>
       <c r="B34" t="n">
-        <v>99614</v>
+        <v>111267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4776,21 +4705,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219880</v>
+        <v>220240</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4808,10 +4737,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500064</v>
+        <v>499993</v>
       </c>
       <c r="R34" t="n">
-        <v>7003220</v>
+        <v>7003212</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4875,16 +4804,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849950</t>
+          <t>https://artportalen.se/Sighting/135849913</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135849951</v>
+        <v>135849914</v>
       </c>
       <c r="B35" t="n">
-        <v>99614</v>
+        <v>111267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4892,21 +4821,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219880</v>
+        <v>220240</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4924,10 +4853,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499969</v>
+        <v>500091</v>
       </c>
       <c r="R35" t="n">
-        <v>7003220</v>
+        <v>7003319</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4962,11 +4891,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>I örtrikt stråk på fuktig mark.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4996,45 +4920,53 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849951</t>
+          <t>https://artportalen.se/Sighting/135849914</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135850037</v>
+        <v>135849981</v>
       </c>
       <c r="B36" t="n">
-        <v>108294</v>
+        <v>99293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220083</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -5045,10 +4977,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500000</v>
+        <v>500163</v>
       </c>
       <c r="R36" t="n">
-        <v>7003248</v>
+        <v>7003324</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5083,6 +5015,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 7 blomställningar inom ca 2 x 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5112,45 +5049,53 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850037</t>
+          <t>https://artportalen.se/Sighting/135849981</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135850038</v>
+        <v>135849982</v>
       </c>
       <c r="B37" t="n">
-        <v>108294</v>
+        <v>99293</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220083</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -5161,10 +5106,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500081</v>
+        <v>500144</v>
       </c>
       <c r="R37" t="n">
-        <v>7003252</v>
+        <v>7003322</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5199,6 +5144,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor och 1 blomställning inom ca 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5228,45 +5178,53 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850038</t>
+          <t>https://artportalen.se/Sighting/135849982</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849924</v>
+        <v>135849983</v>
       </c>
       <c r="B38" t="n">
-        <v>108364</v>
+        <v>99293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5277,10 +5235,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500117</v>
+        <v>500119</v>
       </c>
       <c r="R38" t="n">
-        <v>7003169</v>
+        <v>7003315</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5315,6 +5273,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5344,42 +5307,50 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849924</t>
+          <t>https://artportalen.se/Sighting/135849983</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849930</v>
+        <v>135849984</v>
       </c>
       <c r="B39" t="n">
-        <v>108364</v>
+        <v>99293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5393,10 +5364,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499972</v>
+        <v>500113</v>
       </c>
       <c r="R39" t="n">
-        <v>7003221</v>
+        <v>7003294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5431,6 +5402,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor och 1 blomställning inom ca 0,5 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5460,45 +5436,53 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849930</t>
+          <t>https://artportalen.se/Sighting/135849984</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849931</v>
+        <v>135849985</v>
       </c>
       <c r="B40" t="n">
-        <v>108364</v>
+        <v>99293</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5509,10 +5493,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499953</v>
+        <v>500122</v>
       </c>
       <c r="R40" t="n">
-        <v>7003186</v>
+        <v>7003258</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5547,6 +5531,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor och 13 blomställningar inom ca 2 m2 yta i flerskiktad barrblandskog. "Marmorerade" blad med både ljusgröna och mörkare gröna färgnyanser.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5576,42 +5565,50 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849931</t>
+          <t>https://artportalen.se/Sighting/135849985</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135849932</v>
+        <v>135849989</v>
       </c>
       <c r="B41" t="n">
-        <v>108364</v>
+        <v>99293</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -5625,10 +5622,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499988</v>
+        <v>499998</v>
       </c>
       <c r="R41" t="n">
-        <v>7003195</v>
+        <v>7003253</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5663,6 +5660,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Minst 8 plantor och 2 delvis överblommade blomställningar inom ca 1,5 m2 yta i en i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5692,42 +5694,50 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849932</t>
+          <t>https://artportalen.se/Sighting/135849989</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135849933</v>
+        <v>135849990</v>
       </c>
       <c r="B42" t="n">
-        <v>108364</v>
+        <v>99293</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5741,10 +5751,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499981</v>
+        <v>499993</v>
       </c>
       <c r="R42" t="n">
-        <v>7003230</v>
+        <v>7003173</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5779,6 +5789,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor och 20 överblommade/blommande blomställningar inom ca 3 m2 yta i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5794,6 +5809,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
@@ -5808,45 +5828,53 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849933</t>
+          <t>https://artportalen.se/Sighting/135849990</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135849934</v>
+        <v>135849991</v>
       </c>
       <c r="B43" t="n">
-        <v>108364</v>
+        <v>99293</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5857,10 +5885,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500067</v>
+        <v>499998</v>
       </c>
       <c r="R43" t="n">
-        <v>7003318</v>
+        <v>7003174</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5895,6 +5923,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor och 18 blommande/överblommade blomställningar inom ca 5 m2 yta intill ett par aspar i en lucka i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5910,6 +5943,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad barrblandskog med tall, björk, asp, sälg och gråal.</t>
+        </is>
+      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
@@ -5924,45 +5962,53 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849934</t>
+          <t>https://artportalen.se/Sighting/135849991</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135849911</v>
+        <v>135849992</v>
       </c>
       <c r="B44" t="n">
-        <v>111244</v>
+        <v>99293</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -5973,10 +6019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500133</v>
+        <v>499978</v>
       </c>
       <c r="R44" t="n">
-        <v>7003286</v>
+        <v>7003240</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6011,6 +6057,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor och 5 överblommade blomställningar inom ca 1 m2 yta i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6040,59 +6091,71 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849911</t>
+          <t>https://artportalen.se/Sighting/135849992</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135849913</v>
+        <v>135849993</v>
       </c>
       <c r="B45" t="n">
-        <v>111244</v>
+        <v>99293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499993</v>
+        <v>500087</v>
       </c>
       <c r="R45" t="n">
-        <v>7003212</v>
+        <v>7003308</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6127,6 +6190,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor och 3 överblommade blomställningar inom ca 0,5 m2 yta i flerskiktad barrblandskog. Fint marmorerade blad med både ljusgröna och mörkgröna färgtoner.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6156,16 +6224,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849913</t>
+          <t>https://artportalen.se/Sighting/135849993</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135849914</v>
+        <v>135849860</v>
       </c>
       <c r="B46" t="n">
-        <v>111244</v>
+        <v>110037</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6173,21 +6241,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220240</v>
+        <v>221184</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6205,10 +6273,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500091</v>
+        <v>499941</v>
       </c>
       <c r="R46" t="n">
-        <v>7003319</v>
+        <v>7003197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6272,16 +6340,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849914</t>
+          <t>https://artportalen.se/Sighting/135849860</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135850028</v>
+        <v>135850006</v>
       </c>
       <c r="B47" t="n">
-        <v>110240</v>
+        <v>98344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6289,28 +6357,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220294</v>
+        <v>223358</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6321,10 +6389,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499959</v>
+        <v>499967</v>
       </c>
       <c r="R47" t="n">
-        <v>7003236</v>
+        <v>7003113</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6371,7 +6439,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6388,53 +6456,45 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850028</t>
+          <t>https://artportalen.se/Sighting/135850006</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135849981</v>
+        <v>135850007</v>
       </c>
       <c r="B48" t="n">
-        <v>99276</v>
+        <v>98344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6445,10 +6505,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>500163</v>
+        <v>500037</v>
       </c>
       <c r="R48" t="n">
-        <v>7003324</v>
+        <v>7003192</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6483,11 +6543,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 7 blomställningar inom ca 2 x 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6517,53 +6572,45 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849981</t>
+          <t>https://artportalen.se/Sighting/135850007</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135849982</v>
+        <v>135850008</v>
       </c>
       <c r="B49" t="n">
-        <v>99276</v>
+        <v>98344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6574,10 +6621,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500144</v>
+        <v>499982</v>
       </c>
       <c r="R49" t="n">
-        <v>7003322</v>
+        <v>7003226</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6612,11 +6659,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor och 1 blomställning inom ca 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6646,50 +6688,42 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849982</t>
+          <t>https://artportalen.se/Sighting/135850008</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135849983</v>
+        <v>135849906</v>
       </c>
       <c r="B50" t="n">
-        <v>99276</v>
+        <v>101392</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>224885</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -6703,10 +6737,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>500119</v>
+        <v>500014</v>
       </c>
       <c r="R50" t="n">
-        <v>7003315</v>
+        <v>7003143</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6741,11 +6775,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 5 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6758,7 +6787,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6775,16 +6804,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849983</t>
+          <t>https://artportalen.se/Sighting/135849906</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135849984</v>
+        <v>135850019</v>
       </c>
       <c r="B51" t="n">
-        <v>99276</v>
+        <v>79443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6792,39 +6821,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6832,10 +6848,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500113</v>
+        <v>500291</v>
       </c>
       <c r="R51" t="n">
-        <v>7003294</v>
+        <v>7003310</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6872,7 +6888,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 1 blomställning inom ca 0,5 m2 yta i barrblandskog.</t>
+          <t>Långväxta bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6890,6 +6906,26 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
@@ -6904,56 +6940,47 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849984</t>
+          <t>https://artportalen.se/Sighting/135850019</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135849985</v>
+        <v>135849907</v>
       </c>
       <c r="B52" t="n">
-        <v>99276</v>
+        <v>80558</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6961,10 +6988,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500122</v>
+        <v>500245</v>
       </c>
       <c r="R52" t="n">
-        <v>7003258</v>
+        <v>7003286</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7001,7 +7028,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 13 blomställningar inom ca 2 m2 yta i flerskiktad barrblandskog. "Marmorerade" blad med både ljusgröna och mörkare gröna färgnyanser.</t>
+          <t>Lunglav på 2 sälgar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7019,6 +7046,26 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
@@ -7033,16 +7080,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849985</t>
+          <t>https://artportalen.se/Sighting/135849907</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135849989</v>
+        <v>135849980</v>
       </c>
       <c r="B53" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7069,7 +7116,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7079,7 +7126,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -7090,10 +7137,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499998</v>
+        <v>500289</v>
       </c>
       <c r="R53" t="n">
-        <v>7003253</v>
+        <v>7003310</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7130,7 +7177,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 8 plantor och 2 delvis överblommade blomställningar inom ca 1,5 m2 yta i en i flerskiktad barrblandskog.</t>
+          <t>Minst 14 plantor och 5 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7161,2224 +7208,6 @@
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849989</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>135849990</v>
-      </c>
-      <c r="B54" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>499993</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7003173</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor och 20 överblommade/blommande blomställningar inom ca 3 m2 yta i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Flerskiktad barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849990</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>135849991</v>
-      </c>
-      <c r="B55" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>499998</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7003174</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor och 18 blommande/överblommade blomställningar inom ca 5 m2 yta intill ett par aspar i en lucka i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Grandominerad flerskiktad barrblandskog med tall, björk, asp, sälg och gråal.</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849991</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>135849992</v>
-      </c>
-      <c r="B56" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>499978</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7003240</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor och 5 överblommade blomställningar inom ca 1 m2 yta i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849992</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>135849993</v>
-      </c>
-      <c r="B57" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>500087</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7003308</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Minst 53 plantor och 3 överblommade blomställningar inom ca 0,5 m2 yta i flerskiktad barrblandskog. Fint marmorerade blad med både ljusgröna och mörkgröna färgtoner.</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849993</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>135849860</v>
-      </c>
-      <c r="B58" t="n">
-        <v>110014</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>499941</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7003197</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849860</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135849877</v>
-      </c>
-      <c r="B59" t="n">
-        <v>99298</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>499999</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7003182</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849877</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>135849878</v>
-      </c>
-      <c r="B60" t="n">
-        <v>99298</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>500072</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7003303</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849878</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>135850045</v>
-      </c>
-      <c r="B61" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>500086</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7003449</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850045</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>135849892</v>
-      </c>
-      <c r="B62" t="n">
-        <v>99082</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>499919</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7003193</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849892</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>135850006</v>
-      </c>
-      <c r="B63" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>499967</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7003113</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850006</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>135850007</v>
-      </c>
-      <c r="B64" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>500037</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7003192</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850007</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>135850008</v>
-      </c>
-      <c r="B65" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>499982</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7003226</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850008</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>135849904</v>
-      </c>
-      <c r="B66" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>500029</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7003136</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849904</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>135849906</v>
-      </c>
-      <c r="B67" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>500014</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7003143</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849906</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>135850019</v>
-      </c>
-      <c r="B68" t="n">
-        <v>79441</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>500291</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7003310</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran i barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850019</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135849907</v>
-      </c>
-      <c r="B69" t="n">
-        <v>80556</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>500245</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7003286</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Lunglav på 2 sälgar.</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849907</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135849870</v>
-      </c>
-      <c r="B70" t="n">
-        <v>58141</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>500305</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7003332</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849870</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135849980</v>
-      </c>
-      <c r="B71" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>500289</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7003310</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor och 5 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="inlineStr"/>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135849980</t>
         </is>
@@ -9438,24 +7267,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ53"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135849970</v>
+        <v>135849969</v>
       </c>
       <c r="B8" t="n">
         <v>96505</v>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499985</v>
+        <v>499958</v>
       </c>
       <c r="R8" t="n">
-        <v>7003195</v>
+        <v>7003184</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,11 +1429,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk med högörter.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1463,13 +1458,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849970</t>
+          <t>https://artportalen.se/Sighting/135849969</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135849971</v>
+        <v>135849970</v>
       </c>
       <c r="B9" t="n">
         <v>96505</v>
@@ -1508,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499984</v>
+        <v>499985</v>
       </c>
       <c r="R9" t="n">
-        <v>7003226</v>
+        <v>7003195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,6 +1541,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk med högörter.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1575,13 +1575,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849971</t>
+          <t>https://artportalen.se/Sighting/135849970</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849972</v>
+        <v>135849971</v>
       </c>
       <c r="B10" t="n">
         <v>96505</v>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500084</v>
+        <v>499984</v>
       </c>
       <c r="R10" t="n">
-        <v>7003324</v>
+        <v>7003226</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,43 +1687,44 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849972</t>
+          <t>https://artportalen.se/Sighting/135849971</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135850020</v>
+        <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>96505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500159</v>
+        <v>500084</v>
       </c>
       <c r="R11" t="n">
-        <v>7003227</v>
+        <v>7003324</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,26 +1785,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1818,13 +1799,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850020</t>
+          <t>https://artportalen.se/Sighting/135849972</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135850023</v>
+        <v>135850020</v>
       </c>
       <c r="B12" t="n">
         <v>79443</v>
@@ -1862,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499977</v>
+        <v>500159</v>
       </c>
       <c r="R12" t="n">
-        <v>7003248</v>
+        <v>7003227</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,63 +1930,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850023</t>
+          <t>https://artportalen.se/Sighting/135850020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135849850</v>
+        <v>135850023</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499952</v>
+        <v>499977</v>
       </c>
       <c r="R13" t="n">
-        <v>7003158</v>
+        <v>7003248</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,17 +2012,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2071,12 +2039,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2093,63 +2061,54 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849850</t>
+          <t>https://artportalen.se/Sighting/135850023</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849851</v>
+        <v>135850024</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499941</v>
+        <v>500065</v>
       </c>
       <c r="R14" t="n">
-        <v>7003178</v>
+        <v>7003294</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2184,17 +2143,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2213,14 +2168,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2237,63 +2187,54 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849851</t>
+          <t>https://artportalen.se/Sighting/135850024</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849852</v>
+        <v>135850025</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499932</v>
+        <v>500041</v>
       </c>
       <c r="R15" t="n">
-        <v>7003181</v>
+        <v>7003432</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2328,17 +2269,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2359,12 +2296,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2381,63 +2318,58 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849852</t>
+          <t>https://artportalen.se/Sighting/135850025</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849853</v>
+        <v>135849875</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>80563</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499931</v>
+        <v>500189</v>
       </c>
       <c r="R16" t="n">
-        <v>7003183</v>
+        <v>7003310</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2472,17 +2404,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2493,22 +2421,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2525,13 +2453,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849853</t>
+          <t>https://artportalen.se/Sighting/135849875</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849854</v>
+        <v>135849850</v>
       </c>
       <c r="B17" t="n">
         <v>57982</v>
@@ -2578,10 +2506,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499933</v>
+        <v>499952</v>
       </c>
       <c r="R17" t="n">
-        <v>7003184</v>
+        <v>7003158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2618,7 +2546,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), tydligt färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2669,13 +2597,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849854</t>
+          <t>https://artportalen.se/Sighting/135849850</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849855</v>
+        <v>135849851</v>
       </c>
       <c r="B18" t="n">
         <v>57982</v>
@@ -2722,10 +2650,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499931</v>
+        <v>499941</v>
       </c>
       <c r="R18" t="n">
-        <v>7003182</v>
+        <v>7003178</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2813,13 +2741,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849855</t>
+          <t>https://artportalen.se/Sighting/135849851</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849856</v>
+        <v>135849852</v>
       </c>
       <c r="B19" t="n">
         <v>57982</v>
@@ -2866,10 +2794,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499927</v>
+        <v>499932</v>
       </c>
       <c r="R19" t="n">
-        <v>7003186</v>
+        <v>7003181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2906,7 +2834,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2957,13 +2885,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849856</t>
+          <t>https://artportalen.se/Sighting/135849852</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849857</v>
+        <v>135849853</v>
       </c>
       <c r="B20" t="n">
         <v>57982</v>
@@ -3010,10 +2938,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499918</v>
+        <v>499931</v>
       </c>
       <c r="R20" t="n">
-        <v>7003193</v>
+        <v>7003183</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3101,13 +3029,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849857</t>
+          <t>https://artportalen.se/Sighting/135849853</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849858</v>
+        <v>135849854</v>
       </c>
       <c r="B21" t="n">
         <v>57982</v>
@@ -3154,10 +3082,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499918</v>
+        <v>499933</v>
       </c>
       <c r="R21" t="n">
-        <v>7003195</v>
+        <v>7003184</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3194,7 +3122,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran vid en hyggeskant. Precis vid fyndplatsen observerades samtidigt en födosökande hane av tretåig hackspett.</t>
+          <t>Ringhack (savhack), tydligt färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3245,13 +3173,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849858</t>
+          <t>https://artportalen.se/Sighting/135849854</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849859</v>
+        <v>135849855</v>
       </c>
       <c r="B22" t="n">
         <v>57982</v>
@@ -3279,20 +3207,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3309,7 +3229,7 @@
         <v>499931</v>
       </c>
       <c r="R22" t="n">
-        <v>7003195</v>
+        <v>7003182</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3346,7 +3266,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 hane som sågs födosöka på en stående död gran vid en hyggeskant. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3361,6 +3281,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3377,33 +3317,33 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849859</t>
+          <t>https://artportalen.se/Sighting/135849855</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849995</v>
+        <v>135849856</v>
       </c>
       <c r="B23" t="n">
-        <v>58241</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102981</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3411,16 +3351,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3434,10 +3370,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500020</v>
+        <v>499927</v>
       </c>
       <c r="R23" t="n">
-        <v>7003239</v>
+        <v>7003186</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3474,7 +3410,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 1 hussvala med lockläte flygandes över krontaket troligen även födosökande.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3489,6 +3425,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3505,67 +3461,63 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849995</t>
+          <t>https://artportalen.se/Sighting/135849856</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135850013</v>
+        <v>135849857</v>
       </c>
       <c r="B24" t="n">
-        <v>99192</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499967</v>
+        <v>499918</v>
       </c>
       <c r="R24" t="n">
-        <v>7003224</v>
+        <v>7003193</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3600,13 +3552,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3615,9 +3571,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Rik på högörter.</t>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3634,59 +3605,63 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850013</t>
+          <t>https://artportalen.se/Sighting/135849857</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849949</v>
+        <v>135849858</v>
       </c>
       <c r="B25" t="n">
-        <v>99631</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500041</v>
+        <v>499918</v>
       </c>
       <c r="R25" t="n">
-        <v>7003256</v>
+        <v>7003195</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3723,7 +3698,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Relativt rikligt med kransrams här.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran vid en hyggeskant. Precis vid fyndplatsen observerades samtidigt en födosökande hane av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3732,13 +3707,32 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3755,59 +3749,71 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849949</t>
+          <t>https://artportalen.se/Sighting/135849858</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849951</v>
+        <v>135849859</v>
       </c>
       <c r="B26" t="n">
-        <v>99631</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499969</v>
+        <v>499931</v>
       </c>
       <c r="R26" t="n">
-        <v>7003220</v>
+        <v>7003195</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3844,7 +3850,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I örtrikt stråk på fuktig mark.</t>
+          <t>1 hane som sågs födosöka på en stående död gran vid en hyggeskant. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3853,7 +3859,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3876,59 +3881,67 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849951</t>
+          <t>https://artportalen.se/Sighting/135849859</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849924</v>
+        <v>135849995</v>
       </c>
       <c r="B27" t="n">
-        <v>108387</v>
+        <v>58241</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220102</v>
+        <v>102981</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500117</v>
+        <v>500020</v>
       </c>
       <c r="R27" t="n">
-        <v>7003169</v>
+        <v>7003239</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3963,13 +3976,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 1 hussvala med lockläte flygandes över krontaket troligen även födosökande.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3992,59 +4009,67 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849924</t>
+          <t>https://artportalen.se/Sighting/135849995</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849930</v>
+        <v>135849873</v>
       </c>
       <c r="B28" t="n">
-        <v>108387</v>
+        <v>58143</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220102</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499972</v>
+        <v>499976</v>
       </c>
       <c r="R28" t="n">
-        <v>7003221</v>
+        <v>7003189</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4085,13 +4110,17 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog med dominans av gran.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4108,16 +4137,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849930</t>
+          <t>https://artportalen.se/Sighting/135849873</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849931</v>
+        <v>135849867</v>
       </c>
       <c r="B29" t="n">
-        <v>108387</v>
+        <v>58138</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4125,42 +4154,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220102</v>
+        <v>103023</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499953</v>
+        <v>500138</v>
       </c>
       <c r="R29" t="n">
-        <v>7003186</v>
+        <v>7003230</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4195,13 +4232,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4224,16 +4265,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849931</t>
+          <t>https://artportalen.se/Sighting/135849867</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849932</v>
+        <v>135849869</v>
       </c>
       <c r="B30" t="n">
-        <v>108387</v>
+        <v>58138</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,42 +4282,50 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220102</v>
+        <v>103023</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499988</v>
+        <v>499966</v>
       </c>
       <c r="R30" t="n">
-        <v>7003195</v>
+        <v>7003147</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,13 +4360,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4340,16 +4393,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849932</t>
+          <t>https://artportalen.se/Sighting/135849869</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135849933</v>
+        <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>108387</v>
+        <v>99192</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4357,25 +4410,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220102</v>
+        <v>219795</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -4389,10 +4450,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499981</v>
+        <v>499967</v>
       </c>
       <c r="R31" t="n">
-        <v>7003230</v>
+        <v>7003224</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4442,6 +4503,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Rik på högörter.</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4456,16 +4522,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849933</t>
+          <t>https://artportalen.se/Sighting/135850013</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849934</v>
+        <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>108387</v>
+        <v>99631</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,21 +4539,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4505,10 +4571,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500067</v>
+        <v>500034</v>
       </c>
       <c r="R32" t="n">
-        <v>7003318</v>
+        <v>7003139</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4572,16 +4638,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849934</t>
+          <t>https://artportalen.se/Sighting/135849945</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849911</v>
+        <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>111267</v>
+        <v>99631</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,21 +4655,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220240</v>
+        <v>219880</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4621,10 +4687,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500133</v>
+        <v>500041</v>
       </c>
       <c r="R33" t="n">
-        <v>7003286</v>
+        <v>7003256</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4659,6 +4725,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med kransrams här.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4688,16 +4759,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849911</t>
+          <t>https://artportalen.se/Sighting/135849949</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135849913</v>
+        <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>111267</v>
+        <v>99631</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,21 +4776,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220240</v>
+        <v>219880</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4737,10 +4808,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499993</v>
+        <v>500064</v>
       </c>
       <c r="R34" t="n">
-        <v>7003212</v>
+        <v>7003220</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4804,16 +4875,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849913</t>
+          <t>https://artportalen.se/Sighting/135849950</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135849914</v>
+        <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>111267</v>
+        <v>99631</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,21 +4892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220240</v>
+        <v>219880</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4853,10 +4924,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500091</v>
+        <v>499969</v>
       </c>
       <c r="R35" t="n">
-        <v>7003319</v>
+        <v>7003220</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4891,6 +4962,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>I örtrikt stråk på fuktig mark.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4920,53 +4996,45 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849914</t>
+          <t>https://artportalen.se/Sighting/135849951</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135849981</v>
+        <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>99293</v>
+        <v>108317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4977,10 +5045,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500163</v>
+        <v>500000</v>
       </c>
       <c r="R36" t="n">
-        <v>7003324</v>
+        <v>7003248</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5015,11 +5083,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 7 blomställningar inom ca 2 x 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5049,53 +5112,45 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849981</t>
+          <t>https://artportalen.se/Sighting/135850037</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135849982</v>
+        <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>99293</v>
+        <v>108317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -5106,10 +5161,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500144</v>
+        <v>500081</v>
       </c>
       <c r="R37" t="n">
-        <v>7003322</v>
+        <v>7003252</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5144,11 +5199,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor och 1 blomställning inom ca 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5178,53 +5228,45 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849982</t>
+          <t>https://artportalen.se/Sighting/135850038</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849983</v>
+        <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>99293</v>
+        <v>108387</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5235,10 +5277,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500119</v>
+        <v>500117</v>
       </c>
       <c r="R38" t="n">
-        <v>7003315</v>
+        <v>7003169</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5273,11 +5315,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 5 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5307,50 +5344,42 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849983</t>
+          <t>https://artportalen.se/Sighting/135849924</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849984</v>
+        <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>99293</v>
+        <v>108387</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5364,10 +5393,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500113</v>
+        <v>499972</v>
       </c>
       <c r="R39" t="n">
-        <v>7003294</v>
+        <v>7003221</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5402,11 +5431,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor och 1 blomställning inom ca 0,5 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5436,53 +5460,45 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849984</t>
+          <t>https://artportalen.se/Sighting/135849930</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849985</v>
+        <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>99293</v>
+        <v>108387</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5493,10 +5509,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500122</v>
+        <v>499953</v>
       </c>
       <c r="R40" t="n">
-        <v>7003258</v>
+        <v>7003186</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5531,11 +5547,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst 50 plantor och 13 blomställningar inom ca 2 m2 yta i flerskiktad barrblandskog. "Marmorerade" blad med både ljusgröna och mörkare gröna färgnyanser.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5565,50 +5576,42 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849985</t>
+          <t>https://artportalen.se/Sighting/135849931</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135849989</v>
+        <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>99293</v>
+        <v>108387</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -5622,10 +5625,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499998</v>
+        <v>499988</v>
       </c>
       <c r="R41" t="n">
-        <v>7003253</v>
+        <v>7003195</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5660,11 +5663,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Minst 8 plantor och 2 delvis överblommade blomställningar inom ca 1,5 m2 yta i en i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5694,50 +5692,42 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849989</t>
+          <t>https://artportalen.se/Sighting/135849932</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135849990</v>
+        <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>99293</v>
+        <v>108387</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5751,10 +5741,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499993</v>
+        <v>499981</v>
       </c>
       <c r="R42" t="n">
-        <v>7003173</v>
+        <v>7003230</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5789,11 +5779,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor och 20 överblommade/blommande blomställningar inom ca 3 m2 yta i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5809,11 +5794,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
@@ -5828,53 +5808,45 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849990</t>
+          <t>https://artportalen.se/Sighting/135849933</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135849991</v>
+        <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>99293</v>
+        <v>108387</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5885,10 +5857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499998</v>
+        <v>500067</v>
       </c>
       <c r="R43" t="n">
-        <v>7003174</v>
+        <v>7003318</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5923,11 +5895,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor och 18 blommande/överblommade blomställningar inom ca 5 m2 yta intill ett par aspar i en lucka i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5943,11 +5910,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Grandominerad flerskiktad barrblandskog med tall, björk, asp, sälg och gråal.</t>
-        </is>
-      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
@@ -5962,53 +5924,45 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849991</t>
+          <t>https://artportalen.se/Sighting/135849934</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135849992</v>
+        <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>99293</v>
+        <v>111267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -6019,10 +5973,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499978</v>
+        <v>500133</v>
       </c>
       <c r="R44" t="n">
-        <v>7003240</v>
+        <v>7003286</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6057,11 +6011,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor och 5 överblommade blomställningar inom ca 1 m2 yta i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6091,71 +6040,59 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849992</t>
+          <t>https://artportalen.se/Sighting/135849911</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135849993</v>
+        <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>99293</v>
+        <v>111267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500087</v>
+        <v>499993</v>
       </c>
       <c r="R45" t="n">
-        <v>7003308</v>
+        <v>7003212</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6190,11 +6127,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 53 plantor och 3 överblommade blomställningar inom ca 0,5 m2 yta i flerskiktad barrblandskog. Fint marmorerade blad med både ljusgröna och mörkgröna färgtoner.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6224,16 +6156,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849993</t>
+          <t>https://artportalen.se/Sighting/135849913</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135849860</v>
+        <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>110037</v>
+        <v>111267</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6241,21 +6173,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221184</v>
+        <v>220240</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6273,10 +6205,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499941</v>
+        <v>500091</v>
       </c>
       <c r="R46" t="n">
-        <v>7003197</v>
+        <v>7003319</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6340,16 +6272,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849860</t>
+          <t>https://artportalen.se/Sighting/135849914</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135850006</v>
+        <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>98344</v>
+        <v>110263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6357,28 +6289,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223358</v>
+        <v>220294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6389,10 +6321,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499967</v>
+        <v>499959</v>
       </c>
       <c r="R47" t="n">
-        <v>7003113</v>
+        <v>7003236</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6439,7 +6371,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6456,45 +6388,53 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850006</t>
+          <t>https://artportalen.se/Sighting/135850028</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135850007</v>
+        <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>98344</v>
+        <v>99293</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6505,10 +6445,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>500037</v>
+        <v>500163</v>
       </c>
       <c r="R48" t="n">
-        <v>7003192</v>
+        <v>7003324</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6543,6 +6483,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 7 blomställningar inom ca 2 x 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6572,45 +6517,53 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850007</t>
+          <t>https://artportalen.se/Sighting/135849981</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135850008</v>
+        <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>98344</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6621,10 +6574,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499982</v>
+        <v>500144</v>
       </c>
       <c r="R49" t="n">
-        <v>7003226</v>
+        <v>7003322</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6659,6 +6612,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor och 1 blomställning inom ca 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6688,42 +6646,50 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850008</t>
+          <t>https://artportalen.se/Sighting/135849982</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135849906</v>
+        <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>101392</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>224885</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -6737,10 +6703,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>500014</v>
+        <v>500119</v>
       </c>
       <c r="R50" t="n">
-        <v>7003143</v>
+        <v>7003315</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6775,6 +6741,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6787,7 +6758,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6804,16 +6775,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849906</t>
+          <t>https://artportalen.se/Sighting/135849983</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135850019</v>
+        <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>79443</v>
+        <v>99293</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6821,26 +6792,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6848,10 +6832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500291</v>
+        <v>500113</v>
       </c>
       <c r="R51" t="n">
-        <v>7003310</v>
+        <v>7003294</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6888,7 +6872,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i barrblandskog.</t>
+          <t>Minst 22 plantor och 1 blomställning inom ca 0,5 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6906,26 +6890,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
@@ -6940,47 +6904,56 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850019</t>
+          <t>https://artportalen.se/Sighting/135849984</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135849907</v>
+        <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>80558</v>
+        <v>99293</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6988,10 +6961,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500245</v>
+        <v>500122</v>
       </c>
       <c r="R52" t="n">
-        <v>7003286</v>
+        <v>7003258</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7028,7 +7001,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Lunglav på 2 sälgar.</t>
+          <t>Minst 50 plantor och 13 blomställningar inom ca 2 m2 yta i flerskiktad barrblandskog. "Marmorerade" blad med både ljusgröna och mörkare gröna färgnyanser.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7046,26 +7019,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
@@ -7080,13 +7033,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849907</t>
+          <t>https://artportalen.se/Sighting/135849985</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135849980</v>
+        <v>135849989</v>
       </c>
       <c r="B53" t="n">
         <v>99293</v>
@@ -7116,7 +7069,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7126,7 +7079,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -7137,10 +7090,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500289</v>
+        <v>499998</v>
       </c>
       <c r="R53" t="n">
-        <v>7003310</v>
+        <v>7003253</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7177,7 +7130,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 14 plantor och 5 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 8 plantor och 2 delvis överblommade blomställningar inom ca 1,5 m2 yta i en i flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7208,6 +7161,2224 @@
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849989</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135849990</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>499993</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7003173</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor och 20 överblommade/blommande blomställningar inom ca 3 m2 yta i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849990</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135849991</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>499998</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7003174</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor och 18 blommande/överblommade blomställningar inom ca 5 m2 yta intill ett par aspar i en lucka i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad barrblandskog med tall, björk, asp, sälg och gråal.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849991</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135849992</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>499978</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7003240</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor och 5 överblommade blomställningar inom ca 1 m2 yta i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849992</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135849993</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>500087</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7003308</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor och 3 överblommade blomställningar inom ca 0,5 m2 yta i flerskiktad barrblandskog. Fint marmorerade blad med både ljusgröna och mörkgröna färgtoner.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849993</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135849860</v>
+      </c>
+      <c r="B58" t="n">
+        <v>110037</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>499941</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7003197</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849860</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135849877</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99315</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>499999</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7003182</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849877</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135849878</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99315</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>500072</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7003303</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849878</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135850045</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>500086</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7003449</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850045</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135849892</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>499919</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7003193</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849892</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135850006</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>499967</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7003113</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850006</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135850007</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>500037</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7003192</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850007</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135850008</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>499982</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7003226</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850008</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135849904</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>500029</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7003136</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849904</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135849906</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>500014</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7003143</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849906</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135850019</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>500291</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7003310</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850019</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135849907</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80558</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>500245</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7003286</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Lunglav på 2 sälgar.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849907</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135849870</v>
+      </c>
+      <c r="B70" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>500305</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7003332</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849870</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135849980</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>500289</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7003310</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Minst 14 plantor och 5 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135849980</t>
         </is>
@@ -7267,6 +9438,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849963</v>
       </c>
       <c r="B2" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849964</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849965</v>
       </c>
       <c r="B4" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849966</v>
       </c>
       <c r="B5" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849967</v>
       </c>
       <c r="B6" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849968</v>
       </c>
       <c r="B7" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849969</v>
       </c>
       <c r="B8" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135849970</v>
       </c>
       <c r="B9" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135849971</v>
       </c>
       <c r="B10" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135850020</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>135850023</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135850024</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135850025</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>135849875</v>
       </c>
       <c r="B16" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>99192</v>
+        <v>99193</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>110263</v>
+        <v>110265</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>135849989</v>
       </c>
       <c r="B53" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135849990</v>
       </c>
       <c r="B54" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>135849991</v>
       </c>
       <c r="B55" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>135849992</v>
       </c>
       <c r="B56" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>135849993</v>
       </c>
       <c r="B57" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>135849860</v>
       </c>
       <c r="B58" t="n">
-        <v>110037</v>
+        <v>110039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>135849877</v>
       </c>
       <c r="B59" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135849878</v>
       </c>
       <c r="B60" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135850045</v>
       </c>
       <c r="B61" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>135849892</v>
       </c>
       <c r="B62" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>135850006</v>
       </c>
       <c r="B63" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>135850007</v>
       </c>
       <c r="B64" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>135850008</v>
       </c>
       <c r="B65" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>135849904</v>
       </c>
       <c r="B66" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>135849906</v>
       </c>
       <c r="B67" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>135850019</v>
       </c>
       <c r="B68" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>135849907</v>
       </c>
       <c r="B69" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>135849980</v>
       </c>
       <c r="B71" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ71"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135849969</v>
+        <v>135849970</v>
       </c>
       <c r="B8" t="n">
         <v>96506</v>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499958</v>
+        <v>499985</v>
       </c>
       <c r="R8" t="n">
-        <v>7003184</v>
+        <v>7003195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,6 +1429,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk med högörter.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1458,13 +1463,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849969</t>
+          <t>https://artportalen.se/Sighting/135849970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135849970</v>
+        <v>135849971</v>
       </c>
       <c r="B9" t="n">
         <v>96506</v>
@@ -1503,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499985</v>
+        <v>499984</v>
       </c>
       <c r="R9" t="n">
-        <v>7003195</v>
+        <v>7003226</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,11 +1546,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk med högörter.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1575,13 +1575,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849970</t>
+          <t>https://artportalen.se/Sighting/135849971</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849971</v>
+        <v>135849972</v>
       </c>
       <c r="B10" t="n">
         <v>96506</v>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499984</v>
+        <v>500084</v>
       </c>
       <c r="R10" t="n">
-        <v>7003226</v>
+        <v>7003324</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,44 +1687,43 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849971</t>
+          <t>https://artportalen.se/Sighting/135849972</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135849972</v>
+        <v>135850020</v>
       </c>
       <c r="B11" t="n">
-        <v>96506</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2812</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1732,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500084</v>
+        <v>500159</v>
       </c>
       <c r="R11" t="n">
-        <v>7003324</v>
+        <v>7003227</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,6 +1784,26 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1799,13 +1818,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849972</t>
+          <t>https://artportalen.se/Sighting/135850020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135850020</v>
+        <v>135850023</v>
       </c>
       <c r="B12" t="n">
         <v>79444</v>
@@ -1843,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500159</v>
+        <v>499977</v>
       </c>
       <c r="R12" t="n">
-        <v>7003227</v>
+        <v>7003248</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,54 +1949,63 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850020</t>
+          <t>https://artportalen.se/Sighting/135850023</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135850023</v>
+        <v>135849850</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499977</v>
+        <v>499952</v>
       </c>
       <c r="R13" t="n">
-        <v>7003248</v>
+        <v>7003158</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,13 +2040,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2039,12 +2071,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2061,54 +2093,63 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850023</t>
+          <t>https://artportalen.se/Sighting/135849850</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135850024</v>
+        <v>135849851</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500065</v>
+        <v>499941</v>
       </c>
       <c r="R14" t="n">
-        <v>7003294</v>
+        <v>7003178</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,13 +2184,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2168,9 +2213,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2187,54 +2237,63 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850024</t>
+          <t>https://artportalen.se/Sighting/135849851</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135850025</v>
+        <v>135849852</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500041</v>
+        <v>499932</v>
       </c>
       <c r="R15" t="n">
-        <v>7003432</v>
+        <v>7003181</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,13 +2328,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2296,12 +2359,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2318,58 +2381,63 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850025</t>
+          <t>https://artportalen.se/Sighting/135849852</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849875</v>
+        <v>135849853</v>
       </c>
       <c r="B16" t="n">
-        <v>80564</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500189</v>
+        <v>499931</v>
       </c>
       <c r="R16" t="n">
-        <v>7003310</v>
+        <v>7003183</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2404,13 +2472,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2421,22 +2493,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2453,13 +2525,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849875</t>
+          <t>https://artportalen.se/Sighting/135849853</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849850</v>
+        <v>135849854</v>
       </c>
       <c r="B17" t="n">
         <v>57982</v>
@@ -2506,10 +2578,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499952</v>
+        <v>499933</v>
       </c>
       <c r="R17" t="n">
-        <v>7003158</v>
+        <v>7003184</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2546,7 +2618,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), tydligt färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2597,13 +2669,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849850</t>
+          <t>https://artportalen.se/Sighting/135849854</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849851</v>
+        <v>135849855</v>
       </c>
       <c r="B18" t="n">
         <v>57982</v>
@@ -2650,10 +2722,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499941</v>
+        <v>499931</v>
       </c>
       <c r="R18" t="n">
-        <v>7003178</v>
+        <v>7003182</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2741,13 +2813,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849851</t>
+          <t>https://artportalen.se/Sighting/135849855</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849852</v>
+        <v>135849856</v>
       </c>
       <c r="B19" t="n">
         <v>57982</v>
@@ -2794,10 +2866,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499932</v>
+        <v>499927</v>
       </c>
       <c r="R19" t="n">
-        <v>7003181</v>
+        <v>7003186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2834,7 +2906,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,13 +2957,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849852</t>
+          <t>https://artportalen.se/Sighting/135849856</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849853</v>
+        <v>135849857</v>
       </c>
       <c r="B20" t="n">
         <v>57982</v>
@@ -2938,10 +3010,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499931</v>
+        <v>499918</v>
       </c>
       <c r="R20" t="n">
-        <v>7003183</v>
+        <v>7003193</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3029,13 +3101,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849853</t>
+          <t>https://artportalen.se/Sighting/135849857</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849854</v>
+        <v>135849858</v>
       </c>
       <c r="B21" t="n">
         <v>57982</v>
@@ -3082,10 +3154,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499933</v>
+        <v>499918</v>
       </c>
       <c r="R21" t="n">
-        <v>7003184</v>
+        <v>7003195</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3122,7 +3194,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), tydligt färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran vid en hyggeskant. Precis vid fyndplatsen observerades samtidigt en födosökande hane av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3173,13 +3245,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849854</t>
+          <t>https://artportalen.se/Sighting/135849858</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849855</v>
+        <v>135849859</v>
       </c>
       <c r="B22" t="n">
         <v>57982</v>
@@ -3207,12 +3279,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3229,7 +3309,7 @@
         <v>499931</v>
       </c>
       <c r="R22" t="n">
-        <v>7003182</v>
+        <v>7003195</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3266,7 +3346,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>1 hane som sågs födosöka på en stående död gran vid en hyggeskant. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3281,26 +3361,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3317,33 +3377,33 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849855</t>
+          <t>https://artportalen.se/Sighting/135849859</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849856</v>
+        <v>135849995</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>58241</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102981</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3351,12 +3411,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3370,10 +3434,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499927</v>
+        <v>500020</v>
       </c>
       <c r="R23" t="n">
-        <v>7003186</v>
+        <v>7003239</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3410,7 +3474,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 1 hussvala med lockläte flygandes över krontaket troligen även födosökande.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3425,26 +3489,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3461,63 +3505,67 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849856</t>
+          <t>https://artportalen.se/Sighting/135849995</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849857</v>
+        <v>135850013</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>99193</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>219795</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499918</v>
+        <v>499967</v>
       </c>
       <c r="R24" t="n">
-        <v>7003193</v>
+        <v>7003224</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3552,17 +3600,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3571,24 +3615,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Rik på högörter.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3605,63 +3634,59 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849857</t>
+          <t>https://artportalen.se/Sighting/135850013</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849858</v>
+        <v>135849949</v>
       </c>
       <c r="B25" t="n">
-        <v>57982</v>
+        <v>99632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499918</v>
+        <v>500041</v>
       </c>
       <c r="R25" t="n">
-        <v>7003195</v>
+        <v>7003256</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3698,7 +3723,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran vid en hyggeskant. Precis vid fyndplatsen observerades samtidigt en födosökande hane av tretåig hackspett.</t>
+          <t>Relativt rikligt med kransrams här.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3707,32 +3732,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3749,71 +3755,59 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849858</t>
+          <t>https://artportalen.se/Sighting/135849949</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849859</v>
+        <v>135849951</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>99632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499931</v>
+        <v>499969</v>
       </c>
       <c r="R26" t="n">
-        <v>7003195</v>
+        <v>7003220</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3850,7 +3844,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 hane som sågs födosöka på en stående död gran vid en hyggeskant. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>I örtrikt stråk på fuktig mark.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3859,6 +3853,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3881,67 +3876,59 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849859</t>
+          <t>https://artportalen.se/Sighting/135849951</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849995</v>
+        <v>135849924</v>
       </c>
       <c r="B27" t="n">
-        <v>58241</v>
+        <v>108389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102981</v>
+        <v>220102</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500020</v>
+        <v>500117</v>
       </c>
       <c r="R27" t="n">
-        <v>7003239</v>
+        <v>7003169</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3976,17 +3963,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 1 hussvala med lockläte flygandes över krontaket troligen även födosökande.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4009,67 +3992,59 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849995</t>
+          <t>https://artportalen.se/Sighting/135849924</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849873</v>
+        <v>135849930</v>
       </c>
       <c r="B28" t="n">
-        <v>58143</v>
+        <v>108389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220102</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499976</v>
+        <v>499972</v>
       </c>
       <c r="R28" t="n">
-        <v>7003189</v>
+        <v>7003221</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4110,17 +4085,13 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Flerskiktad barrblandskog med dominans av gran.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4137,16 +4108,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849873</t>
+          <t>https://artportalen.se/Sighting/135849930</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849867</v>
+        <v>135849931</v>
       </c>
       <c r="B29" t="n">
-        <v>58138</v>
+        <v>108389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4154,50 +4125,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103023</v>
+        <v>220102</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500138</v>
+        <v>499953</v>
       </c>
       <c r="R29" t="n">
-        <v>7003230</v>
+        <v>7003186</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4232,17 +4195,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4265,16 +4224,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849867</t>
+          <t>https://artportalen.se/Sighting/135849931</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849869</v>
+        <v>135849932</v>
       </c>
       <c r="B30" t="n">
-        <v>58138</v>
+        <v>108389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4282,50 +4241,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103023</v>
+        <v>220102</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499966</v>
+        <v>499988</v>
       </c>
       <c r="R30" t="n">
-        <v>7003147</v>
+        <v>7003195</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4360,17 +4311,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4393,16 +4340,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849869</t>
+          <t>https://artportalen.se/Sighting/135849932</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135850013</v>
+        <v>135849933</v>
       </c>
       <c r="B31" t="n">
-        <v>99193</v>
+        <v>108389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4410,33 +4357,25 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219795</v>
+        <v>220102</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -4450,10 +4389,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499967</v>
+        <v>499981</v>
       </c>
       <c r="R31" t="n">
-        <v>7003224</v>
+        <v>7003230</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4503,11 +4442,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Rik på högörter.</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4522,16 +4456,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850013</t>
+          <t>https://artportalen.se/Sighting/135849933</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849945</v>
+        <v>135849934</v>
       </c>
       <c r="B32" t="n">
-        <v>99632</v>
+        <v>108389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4539,21 +4473,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4571,10 +4505,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500034</v>
+        <v>500067</v>
       </c>
       <c r="R32" t="n">
-        <v>7003139</v>
+        <v>7003318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4638,16 +4572,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849945</t>
+          <t>https://artportalen.se/Sighting/135849934</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849949</v>
+        <v>135849911</v>
       </c>
       <c r="B33" t="n">
-        <v>99632</v>
+        <v>111269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4655,21 +4589,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219880</v>
+        <v>220240</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4687,10 +4621,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500041</v>
+        <v>500133</v>
       </c>
       <c r="R33" t="n">
-        <v>7003256</v>
+        <v>7003286</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4725,11 +4659,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med kransrams här.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4759,16 +4688,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849949</t>
+          <t>https://artportalen.se/Sighting/135849911</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135849950</v>
+        <v>135849913</v>
       </c>
       <c r="B34" t="n">
-        <v>99632</v>
+        <v>111269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4776,21 +4705,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219880</v>
+        <v>220240</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4808,10 +4737,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500064</v>
+        <v>499993</v>
       </c>
       <c r="R34" t="n">
-        <v>7003220</v>
+        <v>7003212</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4875,16 +4804,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849950</t>
+          <t>https://artportalen.se/Sighting/135849913</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135849951</v>
+        <v>135849914</v>
       </c>
       <c r="B35" t="n">
-        <v>99632</v>
+        <v>111269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4892,21 +4821,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219880</v>
+        <v>220240</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4924,10 +4853,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499969</v>
+        <v>500091</v>
       </c>
       <c r="R35" t="n">
-        <v>7003220</v>
+        <v>7003319</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4962,11 +4891,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>I örtrikt stråk på fuktig mark.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4996,45 +4920,53 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849951</t>
+          <t>https://artportalen.se/Sighting/135849914</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135850037</v>
+        <v>135849981</v>
       </c>
       <c r="B36" t="n">
-        <v>108319</v>
+        <v>99294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220083</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -5045,10 +4977,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500000</v>
+        <v>500163</v>
       </c>
       <c r="R36" t="n">
-        <v>7003248</v>
+        <v>7003324</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5083,6 +5015,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 7 blomställningar inom ca 2 x 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5112,45 +5049,53 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850037</t>
+          <t>https://artportalen.se/Sighting/135849981</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135850038</v>
+        <v>135849982</v>
       </c>
       <c r="B37" t="n">
-        <v>108319</v>
+        <v>99294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220083</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -5161,10 +5106,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500081</v>
+        <v>500144</v>
       </c>
       <c r="R37" t="n">
-        <v>7003252</v>
+        <v>7003322</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5199,6 +5144,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor och 1 blomställning inom ca 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5228,45 +5178,53 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850038</t>
+          <t>https://artportalen.se/Sighting/135849982</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849924</v>
+        <v>135849983</v>
       </c>
       <c r="B38" t="n">
-        <v>108389</v>
+        <v>99294</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5277,10 +5235,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500117</v>
+        <v>500119</v>
       </c>
       <c r="R38" t="n">
-        <v>7003169</v>
+        <v>7003315</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5315,6 +5273,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5344,42 +5307,50 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849924</t>
+          <t>https://artportalen.se/Sighting/135849983</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849930</v>
+        <v>135849984</v>
       </c>
       <c r="B39" t="n">
-        <v>108389</v>
+        <v>99294</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5393,10 +5364,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499972</v>
+        <v>500113</v>
       </c>
       <c r="R39" t="n">
-        <v>7003221</v>
+        <v>7003294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5431,6 +5402,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor och 1 blomställning inom ca 0,5 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5460,45 +5436,53 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849930</t>
+          <t>https://artportalen.se/Sighting/135849984</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849931</v>
+        <v>135849985</v>
       </c>
       <c r="B40" t="n">
-        <v>108389</v>
+        <v>99294</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5509,10 +5493,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499953</v>
+        <v>500122</v>
       </c>
       <c r="R40" t="n">
-        <v>7003186</v>
+        <v>7003258</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5547,6 +5531,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor och 13 blomställningar inom ca 2 m2 yta i flerskiktad barrblandskog. "Marmorerade" blad med både ljusgröna och mörkare gröna färgnyanser.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5576,42 +5565,50 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849931</t>
+          <t>https://artportalen.se/Sighting/135849985</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135849932</v>
+        <v>135849989</v>
       </c>
       <c r="B41" t="n">
-        <v>108389</v>
+        <v>99294</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -5625,10 +5622,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499988</v>
+        <v>499998</v>
       </c>
       <c r="R41" t="n">
-        <v>7003195</v>
+        <v>7003253</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5663,6 +5660,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Minst 8 plantor och 2 delvis överblommade blomställningar inom ca 1,5 m2 yta i en i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5692,42 +5694,50 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849932</t>
+          <t>https://artportalen.se/Sighting/135849989</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135849933</v>
+        <v>135849990</v>
       </c>
       <c r="B42" t="n">
-        <v>108389</v>
+        <v>99294</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5741,10 +5751,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499981</v>
+        <v>499993</v>
       </c>
       <c r="R42" t="n">
-        <v>7003230</v>
+        <v>7003173</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5779,6 +5789,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor och 20 överblommade/blommande blomställningar inom ca 3 m2 yta i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5794,6 +5809,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
@@ -5808,45 +5828,53 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849933</t>
+          <t>https://artportalen.se/Sighting/135849990</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135849934</v>
+        <v>135849991</v>
       </c>
       <c r="B43" t="n">
-        <v>108389</v>
+        <v>99294</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5857,10 +5885,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500067</v>
+        <v>499998</v>
       </c>
       <c r="R43" t="n">
-        <v>7003318</v>
+        <v>7003174</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5895,6 +5923,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor och 18 blommande/överblommade blomställningar inom ca 5 m2 yta intill ett par aspar i en lucka i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5910,6 +5943,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad barrblandskog med tall, björk, asp, sälg och gråal.</t>
+        </is>
+      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
@@ -5924,45 +5962,53 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849934</t>
+          <t>https://artportalen.se/Sighting/135849991</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135849911</v>
+        <v>135849992</v>
       </c>
       <c r="B44" t="n">
-        <v>111269</v>
+        <v>99294</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -5973,10 +6019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500133</v>
+        <v>499978</v>
       </c>
       <c r="R44" t="n">
-        <v>7003286</v>
+        <v>7003240</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6011,6 +6057,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor och 5 överblommade blomställningar inom ca 1 m2 yta i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6040,59 +6091,71 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849911</t>
+          <t>https://artportalen.se/Sighting/135849992</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135849913</v>
+        <v>135849993</v>
       </c>
       <c r="B45" t="n">
-        <v>111269</v>
+        <v>99294</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499993</v>
+        <v>500087</v>
       </c>
       <c r="R45" t="n">
-        <v>7003212</v>
+        <v>7003308</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6127,6 +6190,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor och 3 överblommade blomställningar inom ca 0,5 m2 yta i flerskiktad barrblandskog. Fint marmorerade blad med både ljusgröna och mörkgröna färgtoner.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6156,16 +6224,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849913</t>
+          <t>https://artportalen.se/Sighting/135849993</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135849914</v>
+        <v>135849860</v>
       </c>
       <c r="B46" t="n">
-        <v>111269</v>
+        <v>110039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6173,21 +6241,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220240</v>
+        <v>221184</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6205,10 +6273,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500091</v>
+        <v>499941</v>
       </c>
       <c r="R46" t="n">
-        <v>7003319</v>
+        <v>7003197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6272,16 +6340,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849914</t>
+          <t>https://artportalen.se/Sighting/135849860</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135850028</v>
+        <v>135850006</v>
       </c>
       <c r="B47" t="n">
-        <v>110265</v>
+        <v>98345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6289,28 +6357,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220294</v>
+        <v>223358</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6321,10 +6389,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499959</v>
+        <v>499967</v>
       </c>
       <c r="R47" t="n">
-        <v>7003236</v>
+        <v>7003113</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6371,7 +6439,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6388,53 +6456,45 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850028</t>
+          <t>https://artportalen.se/Sighting/135850006</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135849981</v>
+        <v>135850007</v>
       </c>
       <c r="B48" t="n">
-        <v>99294</v>
+        <v>98345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6445,10 +6505,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>500163</v>
+        <v>500037</v>
       </c>
       <c r="R48" t="n">
-        <v>7003324</v>
+        <v>7003192</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6483,11 +6543,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 7 blomställningar inom ca 2 x 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6517,53 +6572,45 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849981</t>
+          <t>https://artportalen.se/Sighting/135850007</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135849982</v>
+        <v>135850008</v>
       </c>
       <c r="B49" t="n">
-        <v>99294</v>
+        <v>98345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6574,10 +6621,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500144</v>
+        <v>499982</v>
       </c>
       <c r="R49" t="n">
-        <v>7003322</v>
+        <v>7003226</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6612,11 +6659,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor och 1 blomställning inom ca 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6646,50 +6688,42 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849982</t>
+          <t>https://artportalen.se/Sighting/135850008</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135849983</v>
+        <v>135849906</v>
       </c>
       <c r="B50" t="n">
-        <v>99294</v>
+        <v>101394</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>224885</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -6703,10 +6737,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>500119</v>
+        <v>500014</v>
       </c>
       <c r="R50" t="n">
-        <v>7003315</v>
+        <v>7003143</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6741,11 +6775,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 5 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6758,7 +6787,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6775,16 +6804,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849983</t>
+          <t>https://artportalen.se/Sighting/135849906</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135849984</v>
+        <v>135850019</v>
       </c>
       <c r="B51" t="n">
-        <v>99294</v>
+        <v>79444</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6792,39 +6821,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6832,10 +6848,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500113</v>
+        <v>500291</v>
       </c>
       <c r="R51" t="n">
-        <v>7003294</v>
+        <v>7003310</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6872,7 +6888,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 1 blomställning inom ca 0,5 m2 yta i barrblandskog.</t>
+          <t>Långväxta bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6890,6 +6906,26 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
@@ -6904,56 +6940,47 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849984</t>
+          <t>https://artportalen.se/Sighting/135850019</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135849985</v>
+        <v>135849907</v>
       </c>
       <c r="B52" t="n">
-        <v>99294</v>
+        <v>80559</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6961,10 +6988,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500122</v>
+        <v>500245</v>
       </c>
       <c r="R52" t="n">
-        <v>7003258</v>
+        <v>7003286</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7001,7 +7028,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 13 blomställningar inom ca 2 m2 yta i flerskiktad barrblandskog. "Marmorerade" blad med både ljusgröna och mörkare gröna färgnyanser.</t>
+          <t>Lunglav på 2 sälgar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7019,6 +7046,26 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
@@ -7033,13 +7080,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849985</t>
+          <t>https://artportalen.se/Sighting/135849907</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135849989</v>
+        <v>135849980</v>
       </c>
       <c r="B53" t="n">
         <v>99294</v>
@@ -7069,7 +7116,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7079,7 +7126,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -7090,10 +7137,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499998</v>
+        <v>500289</v>
       </c>
       <c r="R53" t="n">
-        <v>7003253</v>
+        <v>7003310</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7130,7 +7177,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 8 plantor och 2 delvis överblommade blomställningar inom ca 1,5 m2 yta i en i flerskiktad barrblandskog.</t>
+          <t>Minst 14 plantor och 5 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7161,2224 +7208,6 @@
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849989</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>135849990</v>
-      </c>
-      <c r="B54" t="n">
-        <v>99294</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>499993</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7003173</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor och 20 överblommade/blommande blomställningar inom ca 3 m2 yta i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Flerskiktad barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849990</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>135849991</v>
-      </c>
-      <c r="B55" t="n">
-        <v>99294</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>499998</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7003174</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor och 18 blommande/överblommade blomställningar inom ca 5 m2 yta intill ett par aspar i en lucka i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Grandominerad flerskiktad barrblandskog med tall, björk, asp, sälg och gråal.</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849991</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>135849992</v>
-      </c>
-      <c r="B56" t="n">
-        <v>99294</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>499978</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7003240</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor och 5 överblommade blomställningar inom ca 1 m2 yta i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849992</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>135849993</v>
-      </c>
-      <c r="B57" t="n">
-        <v>99294</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>500087</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7003308</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Minst 53 plantor och 3 överblommade blomställningar inom ca 0,5 m2 yta i flerskiktad barrblandskog. Fint marmorerade blad med både ljusgröna och mörkgröna färgtoner.</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849993</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>135849860</v>
-      </c>
-      <c r="B58" t="n">
-        <v>110039</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>499941</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7003197</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849860</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135849877</v>
-      </c>
-      <c r="B59" t="n">
-        <v>99316</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>499999</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7003182</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849877</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>135849878</v>
-      </c>
-      <c r="B60" t="n">
-        <v>99316</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>500072</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7003303</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849878</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>135850045</v>
-      </c>
-      <c r="B61" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>500086</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7003449</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850045</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>135849892</v>
-      </c>
-      <c r="B62" t="n">
-        <v>99100</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>499919</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7003193</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849892</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>135850006</v>
-      </c>
-      <c r="B63" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>499967</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7003113</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850006</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>135850007</v>
-      </c>
-      <c r="B64" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>500037</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7003192</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850007</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>135850008</v>
-      </c>
-      <c r="B65" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>499982</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7003226</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850008</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>135849904</v>
-      </c>
-      <c r="B66" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>500029</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7003136</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849904</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>135849906</v>
-      </c>
-      <c r="B67" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>500014</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7003143</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849906</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>135850019</v>
-      </c>
-      <c r="B68" t="n">
-        <v>79444</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>500291</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7003310</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran i barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850019</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135849907</v>
-      </c>
-      <c r="B69" t="n">
-        <v>80559</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>500245</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7003286</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Lunglav på 2 sälgar.</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849907</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135849870</v>
-      </c>
-      <c r="B70" t="n">
-        <v>58143</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>500305</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7003332</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849870</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135849980</v>
-      </c>
-      <c r="B71" t="n">
-        <v>99294</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>500289</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7003310</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor och 5 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="inlineStr"/>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135849980</t>
         </is>
@@ -9438,24 +7267,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ53"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135849963</v>
       </c>
       <c r="B2" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849964</v>
       </c>
       <c r="B3" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849965</v>
       </c>
       <c r="B4" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849966</v>
       </c>
       <c r="B5" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849967</v>
       </c>
       <c r="B6" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849968</v>
       </c>
       <c r="B7" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135849970</v>
+        <v>135849969</v>
       </c>
       <c r="B8" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499985</v>
+        <v>499958</v>
       </c>
       <c r="R8" t="n">
-        <v>7003195</v>
+        <v>7003184</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,11 +1429,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk med högörter.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1463,16 +1458,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849970</t>
+          <t>https://artportalen.se/Sighting/135849969</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135849971</v>
+        <v>135849970</v>
       </c>
       <c r="B9" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499984</v>
+        <v>499985</v>
       </c>
       <c r="R9" t="n">
-        <v>7003226</v>
+        <v>7003195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,6 +1541,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk med högörter.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1575,16 +1575,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849971</t>
+          <t>https://artportalen.se/Sighting/135849970</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849972</v>
+        <v>135849971</v>
       </c>
       <c r="B10" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500084</v>
+        <v>499984</v>
       </c>
       <c r="R10" t="n">
-        <v>7003324</v>
+        <v>7003226</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,43 +1687,44 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849972</t>
+          <t>https://artportalen.se/Sighting/135849971</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135850020</v>
+        <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>96507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500159</v>
+        <v>500084</v>
       </c>
       <c r="R11" t="n">
-        <v>7003227</v>
+        <v>7003324</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,26 +1785,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1818,13 +1799,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850020</t>
+          <t>https://artportalen.se/Sighting/135849972</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135850023</v>
+        <v>135850020</v>
       </c>
       <c r="B12" t="n">
         <v>79444</v>
@@ -1862,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499977</v>
+        <v>500159</v>
       </c>
       <c r="R12" t="n">
-        <v>7003248</v>
+        <v>7003227</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,63 +1930,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850023</t>
+          <t>https://artportalen.se/Sighting/135850020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135849850</v>
+        <v>135850023</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499952</v>
+        <v>499977</v>
       </c>
       <c r="R13" t="n">
-        <v>7003158</v>
+        <v>7003248</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,17 +2012,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2071,12 +2039,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2093,63 +2061,54 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849850</t>
+          <t>https://artportalen.se/Sighting/135850023</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849851</v>
+        <v>135850024</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499941</v>
+        <v>500065</v>
       </c>
       <c r="R14" t="n">
-        <v>7003178</v>
+        <v>7003294</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2184,17 +2143,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2213,14 +2168,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2237,63 +2187,54 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849851</t>
+          <t>https://artportalen.se/Sighting/135850024</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849852</v>
+        <v>135850025</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499932</v>
+        <v>500041</v>
       </c>
       <c r="R15" t="n">
-        <v>7003181</v>
+        <v>7003432</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2328,17 +2269,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2359,12 +2296,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2381,63 +2318,58 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849852</t>
+          <t>https://artportalen.se/Sighting/135850025</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849853</v>
+        <v>135849875</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>80564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499931</v>
+        <v>500189</v>
       </c>
       <c r="R16" t="n">
-        <v>7003183</v>
+        <v>7003310</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2472,17 +2404,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2493,22 +2421,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2525,13 +2453,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849853</t>
+          <t>https://artportalen.se/Sighting/135849875</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849854</v>
+        <v>135849850</v>
       </c>
       <c r="B17" t="n">
         <v>57982</v>
@@ -2578,10 +2506,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499933</v>
+        <v>499952</v>
       </c>
       <c r="R17" t="n">
-        <v>7003184</v>
+        <v>7003158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2618,7 +2546,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), tydligt färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2669,13 +2597,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849854</t>
+          <t>https://artportalen.se/Sighting/135849850</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849855</v>
+        <v>135849851</v>
       </c>
       <c r="B18" t="n">
         <v>57982</v>
@@ -2722,10 +2650,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499931</v>
+        <v>499941</v>
       </c>
       <c r="R18" t="n">
-        <v>7003182</v>
+        <v>7003178</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2813,13 +2741,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849855</t>
+          <t>https://artportalen.se/Sighting/135849851</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849856</v>
+        <v>135849852</v>
       </c>
       <c r="B19" t="n">
         <v>57982</v>
@@ -2866,10 +2794,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499927</v>
+        <v>499932</v>
       </c>
       <c r="R19" t="n">
-        <v>7003186</v>
+        <v>7003181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2906,7 +2834,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2957,13 +2885,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849856</t>
+          <t>https://artportalen.se/Sighting/135849852</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849857</v>
+        <v>135849853</v>
       </c>
       <c r="B20" t="n">
         <v>57982</v>
@@ -3010,10 +2938,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499918</v>
+        <v>499931</v>
       </c>
       <c r="R20" t="n">
-        <v>7003193</v>
+        <v>7003183</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3101,13 +3029,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849857</t>
+          <t>https://artportalen.se/Sighting/135849853</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849858</v>
+        <v>135849854</v>
       </c>
       <c r="B21" t="n">
         <v>57982</v>
@@ -3154,10 +3082,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499918</v>
+        <v>499933</v>
       </c>
       <c r="R21" t="n">
-        <v>7003195</v>
+        <v>7003184</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3194,7 +3122,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran vid en hyggeskant. Precis vid fyndplatsen observerades samtidigt en födosökande hane av tretåig hackspett.</t>
+          <t>Ringhack (savhack), tydligt färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3245,13 +3173,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849858</t>
+          <t>https://artportalen.se/Sighting/135849854</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849859</v>
+        <v>135849855</v>
       </c>
       <c r="B22" t="n">
         <v>57982</v>
@@ -3279,20 +3207,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3309,7 +3229,7 @@
         <v>499931</v>
       </c>
       <c r="R22" t="n">
-        <v>7003195</v>
+        <v>7003182</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3346,7 +3266,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 hane som sågs födosöka på en stående död gran vid en hyggeskant. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3361,6 +3281,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3377,33 +3317,33 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849859</t>
+          <t>https://artportalen.se/Sighting/135849855</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849995</v>
+        <v>135849856</v>
       </c>
       <c r="B23" t="n">
-        <v>58241</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102981</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3411,16 +3351,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3434,10 +3370,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500020</v>
+        <v>499927</v>
       </c>
       <c r="R23" t="n">
-        <v>7003239</v>
+        <v>7003186</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3474,7 +3410,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 1 hussvala med lockläte flygandes över krontaket troligen även födosökande.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3489,6 +3425,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3505,67 +3461,63 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849995</t>
+          <t>https://artportalen.se/Sighting/135849856</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135850013</v>
+        <v>135849857</v>
       </c>
       <c r="B24" t="n">
-        <v>99193</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499967</v>
+        <v>499918</v>
       </c>
       <c r="R24" t="n">
-        <v>7003224</v>
+        <v>7003193</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3600,13 +3552,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3615,9 +3571,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Rik på högörter.</t>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3634,59 +3605,63 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850013</t>
+          <t>https://artportalen.se/Sighting/135849857</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849949</v>
+        <v>135849858</v>
       </c>
       <c r="B25" t="n">
-        <v>99632</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500041</v>
+        <v>499918</v>
       </c>
       <c r="R25" t="n">
-        <v>7003256</v>
+        <v>7003195</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3723,7 +3698,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Relativt rikligt med kransrams här.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran vid en hyggeskant. Precis vid fyndplatsen observerades samtidigt en födosökande hane av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3732,13 +3707,32 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3755,59 +3749,71 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849949</t>
+          <t>https://artportalen.se/Sighting/135849858</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849951</v>
+        <v>135849859</v>
       </c>
       <c r="B26" t="n">
-        <v>99632</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499969</v>
+        <v>499931</v>
       </c>
       <c r="R26" t="n">
-        <v>7003220</v>
+        <v>7003195</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3844,7 +3850,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I örtrikt stråk på fuktig mark.</t>
+          <t>1 hane som sågs födosöka på en stående död gran vid en hyggeskant. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3853,7 +3859,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3876,59 +3881,67 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849951</t>
+          <t>https://artportalen.se/Sighting/135849859</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849924</v>
+        <v>135849995</v>
       </c>
       <c r="B27" t="n">
-        <v>108389</v>
+        <v>58241</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220102</v>
+        <v>102981</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500117</v>
+        <v>500020</v>
       </c>
       <c r="R27" t="n">
-        <v>7003169</v>
+        <v>7003239</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3963,13 +3976,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 1 hussvala med lockläte flygandes över krontaket troligen även födosökande.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3992,59 +4009,67 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849924</t>
+          <t>https://artportalen.se/Sighting/135849995</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849930</v>
+        <v>135849873</v>
       </c>
       <c r="B28" t="n">
-        <v>108389</v>
+        <v>58143</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220102</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499972</v>
+        <v>499976</v>
       </c>
       <c r="R28" t="n">
-        <v>7003221</v>
+        <v>7003189</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4085,13 +4110,17 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog med dominans av gran.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4108,16 +4137,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849930</t>
+          <t>https://artportalen.se/Sighting/135849873</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849931</v>
+        <v>135849867</v>
       </c>
       <c r="B29" t="n">
-        <v>108389</v>
+        <v>58138</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4125,42 +4154,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220102</v>
+        <v>103023</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499953</v>
+        <v>500138</v>
       </c>
       <c r="R29" t="n">
-        <v>7003186</v>
+        <v>7003230</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4195,13 +4232,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4224,16 +4265,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849931</t>
+          <t>https://artportalen.se/Sighting/135849867</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849932</v>
+        <v>135849869</v>
       </c>
       <c r="B30" t="n">
-        <v>108389</v>
+        <v>58138</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,42 +4282,50 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220102</v>
+        <v>103023</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499988</v>
+        <v>499966</v>
       </c>
       <c r="R30" t="n">
-        <v>7003195</v>
+        <v>7003147</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,13 +4360,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4340,16 +4393,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849932</t>
+          <t>https://artportalen.se/Sighting/135849869</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135849933</v>
+        <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>108389</v>
+        <v>99194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4357,25 +4410,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220102</v>
+        <v>219795</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -4389,10 +4450,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499981</v>
+        <v>499967</v>
       </c>
       <c r="R31" t="n">
-        <v>7003230</v>
+        <v>7003224</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4442,6 +4503,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Rik på högörter.</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4456,16 +4522,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849933</t>
+          <t>https://artportalen.se/Sighting/135850013</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849934</v>
+        <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>108389</v>
+        <v>99633</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,21 +4539,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4505,10 +4571,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500067</v>
+        <v>500034</v>
       </c>
       <c r="R32" t="n">
-        <v>7003318</v>
+        <v>7003139</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4572,16 +4638,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849934</t>
+          <t>https://artportalen.se/Sighting/135849945</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849911</v>
+        <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>111269</v>
+        <v>99633</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,21 +4655,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220240</v>
+        <v>219880</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4621,10 +4687,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500133</v>
+        <v>500041</v>
       </c>
       <c r="R33" t="n">
-        <v>7003286</v>
+        <v>7003256</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4659,6 +4725,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med kransrams här.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4688,16 +4759,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849911</t>
+          <t>https://artportalen.se/Sighting/135849949</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135849913</v>
+        <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>111269</v>
+        <v>99633</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,21 +4776,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220240</v>
+        <v>219880</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4737,10 +4808,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499993</v>
+        <v>500064</v>
       </c>
       <c r="R34" t="n">
-        <v>7003212</v>
+        <v>7003220</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4804,16 +4875,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849913</t>
+          <t>https://artportalen.se/Sighting/135849950</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135849914</v>
+        <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>111269</v>
+        <v>99633</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,21 +4892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220240</v>
+        <v>219880</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4853,10 +4924,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500091</v>
+        <v>499969</v>
       </c>
       <c r="R35" t="n">
-        <v>7003319</v>
+        <v>7003220</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4891,6 +4962,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>I örtrikt stråk på fuktig mark.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4920,53 +4996,45 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849914</t>
+          <t>https://artportalen.se/Sighting/135849951</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135849981</v>
+        <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>99294</v>
+        <v>108320</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4977,10 +5045,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500163</v>
+        <v>500000</v>
       </c>
       <c r="R36" t="n">
-        <v>7003324</v>
+        <v>7003248</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5015,11 +5083,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 7 blomställningar inom ca 2 x 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5049,53 +5112,45 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849981</t>
+          <t>https://artportalen.se/Sighting/135850037</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135849982</v>
+        <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>99294</v>
+        <v>108320</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -5106,10 +5161,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500144</v>
+        <v>500081</v>
       </c>
       <c r="R37" t="n">
-        <v>7003322</v>
+        <v>7003252</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5144,11 +5199,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor och 1 blomställning inom ca 1 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5178,53 +5228,45 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849982</t>
+          <t>https://artportalen.se/Sighting/135850038</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849983</v>
+        <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>99294</v>
+        <v>108390</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5235,10 +5277,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500119</v>
+        <v>500117</v>
       </c>
       <c r="R38" t="n">
-        <v>7003315</v>
+        <v>7003169</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5273,11 +5315,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 5 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5307,50 +5344,42 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849983</t>
+          <t>https://artportalen.se/Sighting/135849924</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849984</v>
+        <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>99294</v>
+        <v>108390</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5364,10 +5393,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500113</v>
+        <v>499972</v>
       </c>
       <c r="R39" t="n">
-        <v>7003294</v>
+        <v>7003221</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5402,11 +5431,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor och 1 blomställning inom ca 0,5 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5436,53 +5460,45 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849984</t>
+          <t>https://artportalen.se/Sighting/135849930</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849985</v>
+        <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>99294</v>
+        <v>108390</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5493,10 +5509,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500122</v>
+        <v>499953</v>
       </c>
       <c r="R40" t="n">
-        <v>7003258</v>
+        <v>7003186</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5531,11 +5547,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst 50 plantor och 13 blomställningar inom ca 2 m2 yta i flerskiktad barrblandskog. "Marmorerade" blad med både ljusgröna och mörkare gröna färgnyanser.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5565,50 +5576,42 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849985</t>
+          <t>https://artportalen.se/Sighting/135849931</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135849989</v>
+        <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>99294</v>
+        <v>108390</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -5622,10 +5625,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499998</v>
+        <v>499988</v>
       </c>
       <c r="R41" t="n">
-        <v>7003253</v>
+        <v>7003195</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5660,11 +5663,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Minst 8 plantor och 2 delvis överblommade blomställningar inom ca 1,5 m2 yta i en i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5694,50 +5692,42 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849989</t>
+          <t>https://artportalen.se/Sighting/135849932</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135849990</v>
+        <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>99294</v>
+        <v>108390</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5751,10 +5741,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499993</v>
+        <v>499981</v>
       </c>
       <c r="R42" t="n">
-        <v>7003173</v>
+        <v>7003230</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5789,11 +5779,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor och 20 överblommade/blommande blomställningar inom ca 3 m2 yta i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5809,11 +5794,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
@@ -5828,53 +5808,45 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849990</t>
+          <t>https://artportalen.se/Sighting/135849933</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135849991</v>
+        <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>99294</v>
+        <v>108390</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5885,10 +5857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499998</v>
+        <v>500067</v>
       </c>
       <c r="R43" t="n">
-        <v>7003174</v>
+        <v>7003318</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5923,11 +5895,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor och 18 blommande/överblommade blomställningar inom ca 5 m2 yta intill ett par aspar i en lucka i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5943,11 +5910,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Grandominerad flerskiktad barrblandskog med tall, björk, asp, sälg och gråal.</t>
-        </is>
-      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
@@ -5962,53 +5924,45 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849991</t>
+          <t>https://artportalen.se/Sighting/135849934</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135849992</v>
+        <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>99294</v>
+        <v>111270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -6019,10 +5973,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499978</v>
+        <v>500133</v>
       </c>
       <c r="R44" t="n">
-        <v>7003240</v>
+        <v>7003286</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6057,11 +6011,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor och 5 överblommade blomställningar inom ca 1 m2 yta i flerskiktad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6091,71 +6040,59 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849992</t>
+          <t>https://artportalen.se/Sighting/135849911</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135849993</v>
+        <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>99294</v>
+        <v>111270</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500087</v>
+        <v>499993</v>
       </c>
       <c r="R45" t="n">
-        <v>7003308</v>
+        <v>7003212</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6190,11 +6127,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 53 plantor och 3 överblommade blomställningar inom ca 0,5 m2 yta i flerskiktad barrblandskog. Fint marmorerade blad med både ljusgröna och mörkgröna färgtoner.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6224,16 +6156,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849993</t>
+          <t>https://artportalen.se/Sighting/135849913</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135849860</v>
+        <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>110039</v>
+        <v>111270</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6241,21 +6173,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221184</v>
+        <v>220240</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6273,10 +6205,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499941</v>
+        <v>500091</v>
       </c>
       <c r="R46" t="n">
-        <v>7003197</v>
+        <v>7003319</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6340,16 +6272,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849860</t>
+          <t>https://artportalen.se/Sighting/135849914</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135850006</v>
+        <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>98345</v>
+        <v>110266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6357,28 +6289,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223358</v>
+        <v>220294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6389,10 +6321,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499967</v>
+        <v>499959</v>
       </c>
       <c r="R47" t="n">
-        <v>7003113</v>
+        <v>7003236</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6439,7 +6371,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6456,45 +6388,53 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850006</t>
+          <t>https://artportalen.se/Sighting/135850028</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135850007</v>
+        <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>98345</v>
+        <v>99295</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6505,10 +6445,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>500037</v>
+        <v>500163</v>
       </c>
       <c r="R48" t="n">
-        <v>7003192</v>
+        <v>7003324</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6543,6 +6483,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 7 blomställningar inom ca 2 x 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6572,45 +6517,53 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850007</t>
+          <t>https://artportalen.se/Sighting/135849981</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135850008</v>
+        <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>98345</v>
+        <v>99295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6621,10 +6574,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499982</v>
+        <v>500144</v>
       </c>
       <c r="R49" t="n">
-        <v>7003226</v>
+        <v>7003322</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6659,6 +6612,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor och 1 blomställning inom ca 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6688,42 +6646,50 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850008</t>
+          <t>https://artportalen.se/Sighting/135849982</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135849906</v>
+        <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>101394</v>
+        <v>99295</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>224885</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -6737,10 +6703,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>500014</v>
+        <v>500119</v>
       </c>
       <c r="R50" t="n">
-        <v>7003143</v>
+        <v>7003315</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6775,6 +6741,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6787,7 +6758,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6804,16 +6775,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849906</t>
+          <t>https://artportalen.se/Sighting/135849983</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135850019</v>
+        <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>79444</v>
+        <v>99295</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6821,26 +6792,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6848,10 +6832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500291</v>
+        <v>500113</v>
       </c>
       <c r="R51" t="n">
-        <v>7003310</v>
+        <v>7003294</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6888,7 +6872,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i barrblandskog.</t>
+          <t>Minst 22 plantor och 1 blomställning inom ca 0,5 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6906,26 +6890,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
@@ -6940,47 +6904,56 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850019</t>
+          <t>https://artportalen.se/Sighting/135849984</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135849907</v>
+        <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>80559</v>
+        <v>99295</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6988,10 +6961,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500245</v>
+        <v>500122</v>
       </c>
       <c r="R52" t="n">
-        <v>7003286</v>
+        <v>7003258</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7028,7 +7001,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Lunglav på 2 sälgar.</t>
+          <t>Minst 50 plantor och 13 blomställningar inom ca 2 m2 yta i flerskiktad barrblandskog. "Marmorerade" blad med både ljusgröna och mörkare gröna färgnyanser.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7046,26 +7019,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
@@ -7080,16 +7033,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849907</t>
+          <t>https://artportalen.se/Sighting/135849985</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135849980</v>
+        <v>135849989</v>
       </c>
       <c r="B53" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7116,7 +7069,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7126,7 +7079,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -7137,10 +7090,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500289</v>
+        <v>499998</v>
       </c>
       <c r="R53" t="n">
-        <v>7003310</v>
+        <v>7003253</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7177,7 +7130,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 14 plantor och 5 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 8 plantor och 2 delvis överblommade blomställningar inom ca 1,5 m2 yta i en i flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7208,6 +7161,2224 @@
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849989</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135849990</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>499993</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7003173</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor och 20 överblommade/blommande blomställningar inom ca 3 m2 yta i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849990</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135849991</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>499998</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7003174</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor och 18 blommande/överblommade blomställningar inom ca 5 m2 yta intill ett par aspar i en lucka i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad barrblandskog med tall, björk, asp, sälg och gråal.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849991</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135849992</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>499978</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7003240</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor och 5 överblommade blomställningar inom ca 1 m2 yta i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849992</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135849993</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>500087</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7003308</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor och 3 överblommade blomställningar inom ca 0,5 m2 yta i flerskiktad barrblandskog. Fint marmorerade blad med både ljusgröna och mörkgröna färgtoner.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849993</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135849860</v>
+      </c>
+      <c r="B58" t="n">
+        <v>110040</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>499941</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7003197</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849860</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135849877</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>499999</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7003182</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849877</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135849878</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>500072</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7003303</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849878</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135850045</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>500086</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7003449</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850045</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135849892</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99101</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>499919</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7003193</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849892</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135850006</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>499967</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7003113</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850006</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135850007</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>500037</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7003192</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850007</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135850008</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>499982</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7003226</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850008</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135849904</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>500029</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7003136</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849904</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135849906</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>500014</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7003143</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849906</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135850019</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79444</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>500291</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7003310</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850019</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135849907</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80559</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>500245</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7003286</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Lunglav på 2 sälgar.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849907</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135849870</v>
+      </c>
+      <c r="B70" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>500305</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7003332</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849870</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135849980</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>500289</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7003310</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Minst 14 plantor och 5 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135849980</t>
         </is>
@@ -7267,6 +9438,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849963</v>
       </c>
       <c r="B2" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849964</v>
       </c>
       <c r="B3" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849965</v>
       </c>
       <c r="B4" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849966</v>
       </c>
       <c r="B5" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849967</v>
       </c>
       <c r="B6" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849968</v>
       </c>
       <c r="B7" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849969</v>
       </c>
       <c r="B8" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135849970</v>
       </c>
       <c r="B9" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135849971</v>
       </c>
       <c r="B10" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135850020</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>135850023</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135850024</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135850025</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>135849875</v>
       </c>
       <c r="B16" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>135849850</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>135849851</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>135849852</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>135849853</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135849854</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135849855</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>135849856</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>135849857</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135849858</v>
       </c>
       <c r="B25" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135849859</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>135849995</v>
       </c>
       <c r="B27" t="n">
-        <v>58241</v>
+        <v>58242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>135849873</v>
       </c>
       <c r="B28" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135849867</v>
       </c>
       <c r="B29" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>135849869</v>
       </c>
       <c r="B30" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>99194</v>
+        <v>99195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>111270</v>
+        <v>111271</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>111270</v>
+        <v>111271</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>111270</v>
+        <v>111271</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>110266</v>
+        <v>110267</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>135849989</v>
       </c>
       <c r="B53" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135849990</v>
       </c>
       <c r="B54" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>135849991</v>
       </c>
       <c r="B55" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>135849992</v>
       </c>
       <c r="B56" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>135849993</v>
       </c>
       <c r="B57" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>135849860</v>
       </c>
       <c r="B58" t="n">
-        <v>110040</v>
+        <v>110041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>135849877</v>
       </c>
       <c r="B59" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135849878</v>
       </c>
       <c r="B60" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135850045</v>
       </c>
       <c r="B61" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>135849892</v>
       </c>
       <c r="B62" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>135850006</v>
       </c>
       <c r="B63" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>135850007</v>
       </c>
       <c r="B64" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>135850008</v>
       </c>
       <c r="B65" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>135849904</v>
       </c>
       <c r="B66" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>135849906</v>
       </c>
       <c r="B67" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>135850019</v>
       </c>
       <c r="B68" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>135849907</v>
       </c>
       <c r="B69" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>135849870</v>
       </c>
       <c r="B70" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>135849980</v>
       </c>
       <c r="B71" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849963</v>
       </c>
       <c r="B2" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849964</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849965</v>
       </c>
       <c r="B4" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849966</v>
       </c>
       <c r="B5" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849967</v>
       </c>
       <c r="B6" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849968</v>
       </c>
       <c r="B7" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849969</v>
       </c>
       <c r="B8" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135849970</v>
       </c>
       <c r="B9" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135849971</v>
       </c>
       <c r="B10" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135850020</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>135850023</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135850024</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135850025</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>135849875</v>
       </c>
       <c r="B16" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>135849850</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>135849851</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>135849852</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>135849853</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135849854</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135849855</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>135849856</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>135849857</v>
       </c>
       <c r="B24" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135849858</v>
       </c>
       <c r="B25" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135849859</v>
       </c>
       <c r="B26" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>135849995</v>
       </c>
       <c r="B27" t="n">
-        <v>58242</v>
+        <v>58246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>135849873</v>
       </c>
       <c r="B28" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135849867</v>
       </c>
       <c r="B29" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>135849869</v>
       </c>
       <c r="B30" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>99195</v>
+        <v>99201</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>111271</v>
+        <v>111277</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>111271</v>
+        <v>111277</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>111271</v>
+        <v>111277</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>110267</v>
+        <v>110273</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>135849989</v>
       </c>
       <c r="B53" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135849990</v>
       </c>
       <c r="B54" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>135849991</v>
       </c>
       <c r="B55" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>135849992</v>
       </c>
       <c r="B56" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>135849993</v>
       </c>
       <c r="B57" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>135849860</v>
       </c>
       <c r="B58" t="n">
-        <v>110041</v>
+        <v>110047</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>135849877</v>
       </c>
       <c r="B59" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135849878</v>
       </c>
       <c r="B60" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135850045</v>
       </c>
       <c r="B61" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>135849892</v>
       </c>
       <c r="B62" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>135850006</v>
       </c>
       <c r="B63" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>135850007</v>
       </c>
       <c r="B64" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>135850008</v>
       </c>
       <c r="B65" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>135849904</v>
       </c>
       <c r="B66" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>135849906</v>
       </c>
       <c r="B67" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>135850019</v>
       </c>
       <c r="B68" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>135849907</v>
       </c>
       <c r="B69" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>135849870</v>
       </c>
       <c r="B70" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>135849980</v>
       </c>
       <c r="B71" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849963</v>
       </c>
       <c r="B2" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849964</v>
       </c>
       <c r="B3" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849965</v>
       </c>
       <c r="B4" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849966</v>
       </c>
       <c r="B5" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849967</v>
       </c>
       <c r="B6" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849968</v>
       </c>
       <c r="B7" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849969</v>
       </c>
       <c r="B8" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135849970</v>
       </c>
       <c r="B9" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135849971</v>
       </c>
       <c r="B10" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135850020</v>
       </c>
       <c r="B12" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>135850023</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135850024</v>
       </c>
       <c r="B14" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135850025</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>135849875</v>
       </c>
       <c r="B16" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>135849850</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>135849851</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>135849852</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>135849853</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135849854</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135849855</v>
       </c>
       <c r="B22" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>135849856</v>
       </c>
       <c r="B23" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>135849857</v>
       </c>
       <c r="B24" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135849858</v>
       </c>
       <c r="B25" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135849859</v>
       </c>
       <c r="B26" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>135849995</v>
       </c>
       <c r="B27" t="n">
-        <v>58246</v>
+        <v>58247</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>135849873</v>
       </c>
       <c r="B28" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135849867</v>
       </c>
       <c r="B29" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>135849869</v>
       </c>
       <c r="B30" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>99201</v>
+        <v>99202</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>111277</v>
+        <v>111278</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>111277</v>
+        <v>111278</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>111277</v>
+        <v>111278</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>110273</v>
+        <v>110274</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>135849989</v>
       </c>
       <c r="B53" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135849990</v>
       </c>
       <c r="B54" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>135849991</v>
       </c>
       <c r="B55" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>135849992</v>
       </c>
       <c r="B56" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>135849993</v>
       </c>
       <c r="B57" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>135849860</v>
       </c>
       <c r="B58" t="n">
-        <v>110047</v>
+        <v>110048</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>135849877</v>
       </c>
       <c r="B59" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135849878</v>
       </c>
       <c r="B60" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135850045</v>
       </c>
       <c r="B61" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>135849892</v>
       </c>
       <c r="B62" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>135850006</v>
       </c>
       <c r="B63" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>135850007</v>
       </c>
       <c r="B64" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>135850008</v>
       </c>
       <c r="B65" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>135849904</v>
       </c>
       <c r="B66" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>135849906</v>
       </c>
       <c r="B67" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>135850019</v>
       </c>
       <c r="B68" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>135849907</v>
       </c>
       <c r="B69" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>135849870</v>
       </c>
       <c r="B70" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>135849980</v>
       </c>
       <c r="B71" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849963</v>
       </c>
       <c r="B2" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849964</v>
       </c>
       <c r="B3" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849965</v>
       </c>
       <c r="B4" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849966</v>
       </c>
       <c r="B5" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849967</v>
       </c>
       <c r="B6" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849968</v>
       </c>
       <c r="B7" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849969</v>
       </c>
       <c r="B8" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135849970</v>
       </c>
       <c r="B9" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135849971</v>
       </c>
       <c r="B10" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135850020</v>
       </c>
       <c r="B12" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>135850023</v>
       </c>
       <c r="B13" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135850024</v>
       </c>
       <c r="B14" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135850025</v>
       </c>
       <c r="B15" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>135849875</v>
       </c>
       <c r="B16" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>99202</v>
+        <v>99213</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>111278</v>
+        <v>111289</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>111278</v>
+        <v>111289</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>111278</v>
+        <v>111289</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>110274</v>
+        <v>110285</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>135849989</v>
       </c>
       <c r="B53" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135849990</v>
       </c>
       <c r="B54" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>135849991</v>
       </c>
       <c r="B55" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>135849992</v>
       </c>
       <c r="B56" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>135849993</v>
       </c>
       <c r="B57" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>135849860</v>
       </c>
       <c r="B58" t="n">
-        <v>110048</v>
+        <v>110059</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>135849877</v>
       </c>
       <c r="B59" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135849878</v>
       </c>
       <c r="B60" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135850045</v>
       </c>
       <c r="B61" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>135849892</v>
       </c>
       <c r="B62" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>135850006</v>
       </c>
       <c r="B63" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>135850007</v>
       </c>
       <c r="B64" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>135850008</v>
       </c>
       <c r="B65" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>135849904</v>
       </c>
       <c r="B66" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>135849906</v>
       </c>
       <c r="B67" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>135850019</v>
       </c>
       <c r="B68" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>135849907</v>
       </c>
       <c r="B69" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>135849980</v>
       </c>
       <c r="B71" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849963</v>
       </c>
       <c r="B2" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849964</v>
       </c>
       <c r="B3" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849965</v>
       </c>
       <c r="B4" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849966</v>
       </c>
       <c r="B5" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849967</v>
       </c>
       <c r="B6" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849968</v>
       </c>
       <c r="B7" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849969</v>
       </c>
       <c r="B8" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135849970</v>
       </c>
       <c r="B9" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135849971</v>
       </c>
       <c r="B10" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135850020</v>
       </c>
       <c r="B12" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>135850023</v>
       </c>
       <c r="B13" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135850024</v>
       </c>
       <c r="B14" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135850025</v>
       </c>
       <c r="B15" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>135849875</v>
       </c>
       <c r="B16" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>135849850</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>135849851</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>135849852</v>
       </c>
       <c r="B19" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>135849853</v>
       </c>
       <c r="B20" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135849854</v>
       </c>
       <c r="B21" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135849855</v>
       </c>
       <c r="B22" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>135849856</v>
       </c>
       <c r="B23" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>135849857</v>
       </c>
       <c r="B24" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135849858</v>
       </c>
       <c r="B25" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135849859</v>
       </c>
       <c r="B26" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>135849995</v>
       </c>
       <c r="B27" t="n">
-        <v>58247</v>
+        <v>58252</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>135849873</v>
       </c>
       <c r="B28" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135849867</v>
       </c>
       <c r="B29" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>135849869</v>
       </c>
       <c r="B30" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>99213</v>
+        <v>99226</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>111289</v>
+        <v>111302</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>111289</v>
+        <v>111302</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>111289</v>
+        <v>111302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>110285</v>
+        <v>110298</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>135849989</v>
       </c>
       <c r="B53" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135849990</v>
       </c>
       <c r="B54" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>135849991</v>
       </c>
       <c r="B55" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>135849992</v>
       </c>
       <c r="B56" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>135849993</v>
       </c>
       <c r="B57" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>135849860</v>
       </c>
       <c r="B58" t="n">
-        <v>110059</v>
+        <v>110072</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>135849877</v>
       </c>
       <c r="B59" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135849878</v>
       </c>
       <c r="B60" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135850045</v>
       </c>
       <c r="B61" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>135849892</v>
       </c>
       <c r="B62" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>135850006</v>
       </c>
       <c r="B63" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>135850007</v>
       </c>
       <c r="B64" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>135850008</v>
       </c>
       <c r="B65" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>135849904</v>
       </c>
       <c r="B66" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>135849906</v>
       </c>
       <c r="B67" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>135850019</v>
       </c>
       <c r="B68" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>135849907</v>
       </c>
       <c r="B69" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>135849870</v>
       </c>
       <c r="B70" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>135849980</v>
       </c>
       <c r="B71" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849963</v>
       </c>
       <c r="B2" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849964</v>
       </c>
       <c r="B3" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849965</v>
       </c>
       <c r="B4" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849966</v>
       </c>
       <c r="B5" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849967</v>
       </c>
       <c r="B6" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849968</v>
       </c>
       <c r="B7" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849969</v>
       </c>
       <c r="B8" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135849970</v>
       </c>
       <c r="B9" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135849971</v>
       </c>
       <c r="B10" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>99226</v>
+        <v>99227</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>111302</v>
+        <v>111303</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>111302</v>
+        <v>111303</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>111302</v>
+        <v>111303</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>110298</v>
+        <v>110299</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>135849989</v>
       </c>
       <c r="B53" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135849990</v>
       </c>
       <c r="B54" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>135849991</v>
       </c>
       <c r="B55" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>135849992</v>
       </c>
       <c r="B56" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>135849993</v>
       </c>
       <c r="B57" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>135849860</v>
       </c>
       <c r="B58" t="n">
-        <v>110072</v>
+        <v>110073</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>135849877</v>
       </c>
       <c r="B59" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135849878</v>
       </c>
       <c r="B60" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135850045</v>
       </c>
       <c r="B61" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>135849892</v>
       </c>
       <c r="B62" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>135850006</v>
       </c>
       <c r="B63" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>135850007</v>
       </c>
       <c r="B64" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>135850008</v>
       </c>
       <c r="B65" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>135849904</v>
       </c>
       <c r="B66" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>135849906</v>
       </c>
       <c r="B67" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>135849980</v>
       </c>
       <c r="B71" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849963</v>
       </c>
       <c r="B2" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849964</v>
       </c>
       <c r="B3" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849965</v>
       </c>
       <c r="B4" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849966</v>
       </c>
       <c r="B5" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849967</v>
       </c>
       <c r="B6" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849968</v>
       </c>
       <c r="B7" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849969</v>
       </c>
       <c r="B8" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135849970</v>
       </c>
       <c r="B9" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135849971</v>
       </c>
       <c r="B10" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135850020</v>
       </c>
       <c r="B12" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>135850023</v>
       </c>
       <c r="B13" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135850024</v>
       </c>
       <c r="B14" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135850025</v>
       </c>
       <c r="B15" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>135849875</v>
       </c>
       <c r="B16" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>135849850</v>
       </c>
       <c r="B17" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>135849851</v>
       </c>
       <c r="B18" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>135849852</v>
       </c>
       <c r="B19" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>135849853</v>
       </c>
       <c r="B20" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135849854</v>
       </c>
       <c r="B21" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135849855</v>
       </c>
       <c r="B22" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>135849856</v>
       </c>
       <c r="B23" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>135849857</v>
       </c>
       <c r="B24" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135849858</v>
       </c>
       <c r="B25" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135849859</v>
       </c>
       <c r="B26" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>135849995</v>
       </c>
       <c r="B27" t="n">
-        <v>58252</v>
+        <v>58265</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>135849873</v>
       </c>
       <c r="B28" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135849867</v>
       </c>
       <c r="B29" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>135849869</v>
       </c>
       <c r="B30" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>99227</v>
+        <v>99240</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>111303</v>
+        <v>111316</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>111303</v>
+        <v>111316</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>111303</v>
+        <v>111316</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>110299</v>
+        <v>110312</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>135849989</v>
       </c>
       <c r="B53" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135849990</v>
       </c>
       <c r="B54" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>135849991</v>
       </c>
       <c r="B55" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>135849992</v>
       </c>
       <c r="B56" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>135849993</v>
       </c>
       <c r="B57" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>135849860</v>
       </c>
       <c r="B58" t="n">
-        <v>110073</v>
+        <v>110086</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>135849877</v>
       </c>
       <c r="B59" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135849878</v>
       </c>
       <c r="B60" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135850045</v>
       </c>
       <c r="B61" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>135849892</v>
       </c>
       <c r="B62" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>135850006</v>
       </c>
       <c r="B63" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>135850007</v>
       </c>
       <c r="B64" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>135850008</v>
       </c>
       <c r="B65" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>135849904</v>
       </c>
       <c r="B66" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>135849906</v>
       </c>
       <c r="B67" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>135850019</v>
       </c>
       <c r="B68" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>135849907</v>
       </c>
       <c r="B69" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>135849870</v>
       </c>
       <c r="B70" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>135849980</v>
       </c>
       <c r="B71" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 28059-2026 artfynd.xlsx
+++ b/artfynd/A 28059-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849963</v>
       </c>
       <c r="B2" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849964</v>
       </c>
       <c r="B3" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849965</v>
       </c>
       <c r="B4" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849966</v>
       </c>
       <c r="B5" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849967</v>
       </c>
       <c r="B6" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849968</v>
       </c>
       <c r="B7" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849969</v>
       </c>
       <c r="B8" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135849970</v>
       </c>
       <c r="B9" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135849971</v>
       </c>
       <c r="B10" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135849972</v>
       </c>
       <c r="B11" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135850020</v>
       </c>
       <c r="B12" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>135850023</v>
       </c>
       <c r="B13" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135850024</v>
       </c>
       <c r="B14" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135850025</v>
       </c>
       <c r="B15" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>135849875</v>
       </c>
       <c r="B16" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>135850013</v>
       </c>
       <c r="B31" t="n">
-        <v>99240</v>
+        <v>99241</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135849945</v>
       </c>
       <c r="B32" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135849949</v>
       </c>
       <c r="B33" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135849950</v>
       </c>
       <c r="B34" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135849951</v>
       </c>
       <c r="B35" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135850037</v>
       </c>
       <c r="B36" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>135850038</v>
       </c>
       <c r="B37" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135849924</v>
       </c>
       <c r="B38" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>135849930</v>
       </c>
       <c r="B39" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135849931</v>
       </c>
       <c r="B40" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>135849932</v>
       </c>
       <c r="B41" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>135849933</v>
       </c>
       <c r="B42" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>135849934</v>
       </c>
       <c r="B43" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>135849911</v>
       </c>
       <c r="B44" t="n">
-        <v>111316</v>
+        <v>111317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135849913</v>
       </c>
       <c r="B45" t="n">
-        <v>111316</v>
+        <v>111317</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>135849914</v>
       </c>
       <c r="B46" t="n">
-        <v>111316</v>
+        <v>111317</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135850028</v>
       </c>
       <c r="B47" t="n">
-        <v>110312</v>
+        <v>110313</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135849981</v>
       </c>
       <c r="B48" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>135849982</v>
       </c>
       <c r="B49" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>135849983</v>
       </c>
       <c r="B50" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>135849984</v>
       </c>
       <c r="B51" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>135849985</v>
       </c>
       <c r="B52" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>135849989</v>
       </c>
       <c r="B53" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135849990</v>
       </c>
       <c r="B54" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>135849991</v>
       </c>
       <c r="B55" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>135849992</v>
       </c>
       <c r="B56" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>135849993</v>
       </c>
       <c r="B57" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>135849860</v>
       </c>
       <c r="B58" t="n">
-        <v>110086</v>
+        <v>110087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>135849877</v>
       </c>
       <c r="B59" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135849878</v>
       </c>
       <c r="B60" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135850045</v>
       </c>
       <c r="B61" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>135849892</v>
       </c>
       <c r="B62" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>135850006</v>
       </c>
       <c r="B63" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>135850007</v>
       </c>
       <c r="B64" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>135850008</v>
       </c>
       <c r="B65" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>135849904</v>
       </c>
       <c r="B66" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>135849906</v>
       </c>
       <c r="B67" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>135850019</v>
       </c>
       <c r="B68" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>135849907</v>
       </c>
       <c r="B69" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>135849980</v>
       </c>
       <c r="B71" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
